--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.3%</t>
+          <t>782.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.3%</t>
+          <t>-578.8%</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.1%</t>
+          <t>-267.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.6482308864696</v>
+        <v>-9.814368578105228</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7114259850077462</v>
+        <v>-0.7778810616619976</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.608046588103409</v>
+        <v>-9.774184279739037</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6950086417734287</v>
+        <v>-0.76146371842768</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.527976792565605</v>
+        <v>-9.694114484201233</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6636139023375502</v>
+        <v>-0.7300689789918011</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.294495570336007</v>
+        <v>-9.460633261971633</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5622969846078587</v>
+        <v>-0.6287520612621091</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.114787040192134</v>
+        <v>-9.28092473182776</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4933057828632683</v>
+        <v>-0.5597608595175187</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.982511566561246</v>
+        <v>-9.148649258196873</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4450281066638864</v>
+        <v>-0.5114831833181368</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.791911891888093</v>
+        <v>-8.958049583523719</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3659731761069884</v>
+        <v>-0.4324282527612389</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.542912093204512</v>
+        <v>-8.709049784840138</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2534669154098972</v>
+        <v>-0.3199219920641476</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.648502082977616</v>
+        <v>-8.814639774613243</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4236788409183578</v>
+        <v>-0.4901339175726083</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.667236985096213</v>
+        <v>-8.83337467673184</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3826284598887102</v>
+        <v>-0.4490835365429606</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.519296943688614</v>
+        <v>-8.68543463532424</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.443331366013838</v>
+        <v>-0.5097864426680885</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.392404537253544</v>
+        <v>-8.55854222888917</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.401288389693288</v>
+        <v>-0.4677434663475384</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.348856130482853</v>
+        <v>-8.514993822118479</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3908296390801045</v>
+        <v>-0.4572847157343549</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.106707737028994</v>
+        <v>-8.27284542866462</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2795079273174181</v>
+        <v>-0.3459630039716686</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.043478365260647</v>
+        <v>-8.209616056896273</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2596840581508841</v>
+        <v>-0.3261391348051346</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.856990672883641</v>
+        <v>-8.023128364519266</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1875908871895051</v>
+        <v>-0.2540459638437551</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.835841473980198</v>
+        <v>-8.001979165615822</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1714302293908023</v>
+        <v>-0.2378853060450528</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.592076031996753</v>
+        <v>-7.758213723632378</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07814334425037428</v>
+        <v>-0.1445984209046243</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.328047964803494</v>
+        <v>-7.494185656439117</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.02959219654694589</v>
+        <v>-0.0368628801073041</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.078197570854419</v>
+        <v>-7.244335262490043</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1222744291102775</v>
+        <v>0.05581935245602798</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.77463008185044</v>
+        <v>-6.940767773486064</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2473005482325181</v>
+        <v>0.1808454715782681</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.701150172998426</v>
+        <v>-6.86728786463405</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2900200178278771</v>
+        <v>0.2235649411736276</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.476117173329603</v>
+        <v>-6.642254864965227</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3790536953117032</v>
+        <v>0.3125986186574536</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.261482795693197</v>
+        <v>-6.42762048732882</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4696022474205832</v>
+        <v>0.4031471707663337</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.994882438718845</v>
+        <v>-6.161020130354468</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5574366489941198</v>
+        <v>0.4909815723398698</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.754451941913985</v>
+        <v>-5.920589633549608</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6553519243409411</v>
+        <v>0.5888968476866916</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.511661134264539</v>
+        <v>-5.677798825900163</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7563975612355396</v>
+        <v>0.68994248458129</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.395721284639354</v>
+        <v>-5.561858976274977</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8034520850029536</v>
+        <v>0.7369970083487041</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.083467668462009</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.15306569621619</v>
+        <v>-5.319203387851814</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8975123915922127</v>
+        <v>0.8310573149379632</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.083467668462009</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.93304489817918</v>
+        <v>-5.099182589814803</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9870997478176311</v>
+        <v>0.9206446711633816</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9422478233940288</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.733796268274371</v>
+        <v>-4.899933959909994</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.082693382581378</v>
+        <v>1.016238305927128</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9422478233940288</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.574281164755001</v>
+        <v>-4.740418856390624</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.147645268429428</v>
+        <v>1.081190191775178</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7827327198746589</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.429609019655263</v>
+        <v>-4.595746711290887</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.215602229030763</v>
+        <v>1.149147152376513</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6380605747749215</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.411839560724307</v>
+        <v>-4.577977252359931</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.138049704689867</v>
+        <v>1.071594628035617</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6202911158439659</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.325040062945298</v>
+        <v>-4.491177754580922</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.195169997124036</v>
+        <v>1.128714920469787</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6202911158439659</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.225347448216286</v>
+        <v>-4.39148513985191</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.235119444389053</v>
+        <v>1.168664367734804</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5205985011149541</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.293717634540297</v>
+        <v>-4.45985532617592</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.218778292334151</v>
+        <v>1.152323215679901</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5113228020787391</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.17230120491382</v>
+        <v>-4.338438896549444</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.257781572816633</v>
+        <v>1.191326496162383</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5113228020787391</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.203294364242526</v>
+        <v>-4.369432055878149</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.070093874125538</v>
+        <v>1.003638797471288</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5113228020787391</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.027820104450056</v>
+        <v>-4.193957796085679</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.144850810034313</v>
+        <v>1.078395733380064</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5113228020787391</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.824215653694113</v>
+        <v>3.482995180434443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.136953323536403</v>
+        <v>-4.172118318326864</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.101208996286572</v>
+        <v>1.087142998370388</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5113228020787391</v>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-707.4%</t>
+          <t>-696.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>782.5%</t>
+          <t>788.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.8%</t>
+          <t>-564.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.6%</t>
+          <t>-273.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-267.5%</t>
+          <t>-261.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-161.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.1%</t>
+          <t>-268.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.1%</t>
+          <t>-197.3%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.566067901468164</v>
+        <v>-8.457586628664018</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3096214300784204</v>
+        <v>-0.2662289209567614</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.805329234088272</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.996444981640938</v>
+        <v>2.03396461436963</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.9994170095784</v>
+        <v>-8.890935736774253</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4869873778569174</v>
+        <v>-0.4435948687352589</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.805329234088272</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.992418677106535</v>
+        <v>2.029938309835227</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.382418398321031</v>
+        <v>-9.273937125516884</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6402900346755538</v>
+        <v>-0.5968975255538953</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.805329234088272</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.992316575784951</v>
+        <v>2.029836208513643</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.757403724492308</v>
+        <v>-9.648922451688161</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7877126491726347</v>
+        <v>-0.7443201400509758</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.18031456025955</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.769896896053614</v>
+        <v>1.807416528782307</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.11693404699631</v>
+        <v>-10.00845277419216</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9261744748761851</v>
+        <v>-0.8827819657545266</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.18031456025955</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.775247199351664</v>
+        <v>1.812766832080357</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.44333407566132</v>
+        <v>-10.33485280285718</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.048818466385013</v>
+        <v>-1.005425957263354</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.56924731013905</v>
+        <v>-2.506714588924563</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.587323202109834</v>
+        <v>1.624842834838526</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.66248304373552</v>
+        <v>-10.55400177093137</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.133436302992923</v>
+        <v>-1.090043793871264</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.72586355699876</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.458875571887084</v>
+        <v>1.496395204615777</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.65879211877911</v>
+        <v>-10.55031084597496</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.131959933010358</v>
+        <v>-1.0885674238887</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.72586355699876</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.458875571887084</v>
+        <v>1.496395204615777</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.86305029410897</v>
+        <v>-10.75456902130483</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.208150006023661</v>
+        <v>-1.164757496902003</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.916035222827236</v>
+        <v>-2.853502501612749</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.387805402237333</v>
+        <v>1.425325034966026</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.08108806574015</v>
+        <v>-10.972606792936</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.290882560191697</v>
+        <v>-1.247490051070038</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.090805990923135</v>
+        <v>-3.028273269708648</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.28742549586423</v>
+        <v>1.324945128592923</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.0076182340727</v>
+        <v>-10.89913696126855</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.246122926031296</v>
+        <v>-1.202730416909637</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.017336159255687</v>
+        <v>-2.954803438041199</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.34687909635812</v>
+        <v>1.384398729086813</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.18274265145924</v>
+        <v>-11.0742613786551</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.301617472238396</v>
+        <v>-1.258224963116738</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.129927855427743</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.256359666673711</v>
+        <v>1.293879299402403</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.41719474547373</v>
+        <v>-11.30871347266959</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.402617474745788</v>
+        <v>-1.35922496562413</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.129927855427743</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.249140501772115</v>
+        <v>1.286660134500807</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.70499859001097</v>
+        <v>-11.59651731720683</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.52441120333466</v>
+        <v>-1.481018694213001</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.480264421179469</v>
+        <v>-3.417731699964981</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.069786004275796</v>
+        <v>1.107305637004488</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.9348230371748</v>
+        <v>-11.82634176437065</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.615225192361634</v>
+        <v>-1.571832683239975</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.642911958249629</v>
+        <v>-3.580379237035142</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9733132718722559</v>
+        <v>1.010832904600948</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.16685195691106</v>
+        <v>-12.05837068410691</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.705343031627024</v>
+        <v>-1.661950522505366</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.642391934223565</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9387993821883165</v>
+        <v>0.9763190149170087</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.11483644294225</v>
+        <v>-12.0063551701381</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.680546490353098</v>
+        <v>-1.637153981231439</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.642391934223565</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9427897178747173</v>
+        <v>0.9803093506034095</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.25650828466637</v>
+        <v>-12.14802701186222</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.738690453941488</v>
+        <v>-1.695297944819829</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.642391934223565</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9413144909759756</v>
+        <v>0.9788341237046678</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.35541502512564</v>
+        <v>-12.2469337523215</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.763199739960326</v>
+        <v>-1.719807230838667</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.803831395897328</v>
+        <v>-3.74129867468284</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8970238568652826</v>
+        <v>0.9345434895939753</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.15626291788854</v>
+        <v>-12.0477816450844</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.696590030712169</v>
+        <v>-1.65319752159051</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.638508869947514</v>
+        <v>-3.575976148733027</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9831662387884879</v>
+        <v>1.02068587151718</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.93041776516913</v>
+        <v>-11.82193649236499</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.596672896588195</v>
+        <v>-1.553280387466538</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.534049473145863</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.017901317176995</v>
+        <v>1.055420949905687</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.64414295284644</v>
+        <v>-11.53566168004229</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.481023827103059</v>
+        <v>-1.4376313179814</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.534049473145863</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.019040461733054</v>
+        <v>1.056560094461746</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.69703824089072</v>
+        <v>-11.58855696808658</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.499548168158666</v>
+        <v>-1.456155659037008</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.529094127057417</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.024647443548229</v>
+        <v>1.062167076276921</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.41312950996197</v>
+        <v>-11.30464823715783</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.38025097154853</v>
+        <v>-1.336858462426871</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.529094127057417</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.030381147786865</v>
+        <v>1.067900780515558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.29770858582388</v>
+        <v>-11.18922731301973</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.343819864287156</v>
+        <v>-1.300427355165498</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.413673202919322</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.089896439875857</v>
+        <v>1.12741607260455</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.03387171861981</v>
+        <v>-10.92539044581566</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.248168598718436</v>
+        <v>-1.204776089596778</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.413673202919322</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08001295856295</v>
+        <v>1.117532591291643</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.76662991775141</v>
+        <v>-10.65814864494727</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.14310643887045</v>
+        <v>-1.099713929748793</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.413673202919322</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.078178398063576</v>
+        <v>1.115698030792269</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64332398927319</v>
+        <v>-10.53484271646905</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.094084382452623</v>
+        <v>-1.050691873330966</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.386788253006246</v>
+        <v>-3.324255531791759</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.131528685766653</v>
+        <v>1.169048318495346</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61937044829723</v>
+        <v>-10.51088917549309</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083834459916747</v>
+        <v>-1.040441950795089</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.362834712030288</v>
+        <v>-3.300301990815801</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.146569316497721</v>
+        <v>1.184088949226414</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487769</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35531050997444</v>
+        <v>-10.24682923717029</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9914708007493802</v>
+        <v>-0.9480782916277226</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.098774773707492</v>
+        <v>-3.036242052493005</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.291744963329647</v>
+        <v>1.329264596058339</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.814368578105228</v>
+        <v>-9.539749613665455</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7778810616619976</v>
+        <v>-0.6680334758860882</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.098774773707492</v>
+        <v>-3.036242052493005</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.288957929669346</v>
+        <v>1.326477562398038</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.774184279739037</v>
+        <v>-9.499565315299265</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.76146371842768</v>
+        <v>-0.6516161326517707</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.058590475341301</v>
+        <v>-2.996057754126814</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.313412132576902</v>
+        <v>1.350931765305594</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.694114484201233</v>
+        <v>-9.41949551976146</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7300689789918011</v>
+        <v>-0.6202213932158922</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.978520679803497</v>
+        <v>-2.91598795858901</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.360820831120341</v>
+        <v>1.398340463849034</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.460633261971633</v>
+        <v>-9.186014297531862</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6287520612621091</v>
+        <v>-0.5189044754862007</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.745039457573899</v>
+        <v>-2.682506736359411</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.508833993295953</v>
+        <v>1.546353626024645</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.28092473182776</v>
+        <v>-9.006305767387989</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5597608595175187</v>
+        <v>-0.4499132737416103</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.687867953411203</v>
+        <v>-2.625335232196715</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.540244685480611</v>
+        <v>1.577764318209304</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.148649258196873</v>
+        <v>-8.874030293757102</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5114831833181368</v>
+        <v>-0.4016355975422283</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.555592479780316</v>
+        <v>-2.493059758565829</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.61497745640617</v>
+        <v>1.652497089134862</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.958049583523719</v>
+        <v>-8.683430619083948</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4324282527612389</v>
+        <v>-0.3225806669853304</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.302460083892676</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.732152321897698</v>
+        <v>1.769671954626391</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.709049784840138</v>
+        <v>-8.434430820400367</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3199219920641476</v>
+        <v>-0.2100744062882391</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.302460083892676</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.745058663121357</v>
+        <v>1.78257829585005</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.814639774613243</v>
+        <v>-8.540020810173472</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4901339175726083</v>
+        <v>-0.3802863317966998</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.408050073665781</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.553728739658276</v>
+        <v>1.591248372386968</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.83337467673184</v>
+        <v>-8.558755712292069</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4490835365429606</v>
+        <v>-0.3392359507670522</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.408050073665781</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.602273081535362</v>
+        <v>1.639792714264054</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.68543463532424</v>
+        <v>-8.410815670884469</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5097864426680885</v>
+        <v>-0.39993885689218</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.45026187897171</v>
+        <v>-2.387729157757223</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.494586708392329</v>
+        <v>1.532106341121022</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.55854222888917</v>
+        <v>-8.283923264449399</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4677434663475384</v>
+        <v>-0.3578958805716299</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.260836751322153</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.562008165999893</v>
+        <v>1.599527798728585</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.514993822118479</v>
+        <v>-8.240374857678708</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4572847157343549</v>
+        <v>-0.3474371299584469</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.260836751322153</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.5550475539048</v>
+        <v>1.592567186633492</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.27284542866462</v>
+        <v>-7.99822646422485</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3459630039716686</v>
+        <v>-0.2361154181957605</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.260836751322153</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.569509908285943</v>
+        <v>1.607029541014635</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.209616056896273</v>
+        <v>-7.934997092456501</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3261391348051346</v>
+        <v>-0.2162915490292261</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.260836751322153</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.564042028745138</v>
+        <v>1.60156166147383</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.023128364519266</v>
+        <v>-7.748509400079495</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2540459638437551</v>
+        <v>-0.1441983780678466</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.136881780159634</v>
+        <v>-2.074349058945147</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.673432738181919</v>
+        <v>1.710952370910611</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.001979165615822</v>
+        <v>-7.727360201176052</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2378853060450528</v>
+        <v>-0.1280377202691443</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.053199860041703</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.69382323576131</v>
+        <v>1.731342868490002</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.758213723632378</v>
+        <v>-7.483594759192608</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1445984209046243</v>
+        <v>-0.0347508351287158</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.053199860041703</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.689603944108361</v>
+        <v>1.727123576837053</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.494185656439117</v>
+        <v>-7.219566691999347</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0368628801073041</v>
+        <v>0.07298470566860438</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.85133446122575</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.812847497317949</v>
+        <v>1.850367130046641</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.244335262490043</v>
+        <v>-6.969716298050272</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.05581935245602798</v>
+        <v>0.1656669382319365</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.85133446122575</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.805589572301651</v>
+        <v>1.843109205030343</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.940767773486064</v>
+        <v>-6.666148809046294</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1808454715782681</v>
+        <v>0.2906930573541766</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.85133446122575</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.8091886958223</v>
+        <v>1.846708328550992</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.86728786463405</v>
+        <v>-6.59266890019428</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2235649411736276</v>
+        <v>0.333412526949536</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.840387273588223</v>
+        <v>-1.777854552373735</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.866604147188062</v>
+        <v>1.904123779916754</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.642254864965227</v>
+        <v>-6.367635900525457</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3125986186574536</v>
+        <v>0.4224462044333621</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.6153542739194</v>
+        <v>-1.552821552704913</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.000644424605652</v>
+        <v>2.038164057334345</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.42762048732882</v>
+        <v>-6.15300152288905</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4031471707663337</v>
+        <v>0.5129947565422421</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.338187175068506</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.134119852241814</v>
+        <v>2.171639484970506</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.161020130354468</v>
+        <v>-5.886401165914698</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4909815723398698</v>
+        <v>0.6008291581157783</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.338187175068506</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.115314111025609</v>
+        <v>2.152833743754302</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.920589633549608</v>
+        <v>-5.645970669109838</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5888968476866916</v>
+        <v>0.6987444334626001</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.097756678263646</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.261315485733403</v>
+        <v>2.298835118462095</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.677798825900163</v>
+        <v>-5.403179861460393</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.68994248458129</v>
+        <v>0.7997900703571985</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.097756678263646</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.265244799568223</v>
+        <v>2.302764432296915</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.561858976274977</v>
+        <v>-5.287240011835207</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7369970083487041</v>
+        <v>0.8468445941246125</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.083467668462009</v>
+        <v>-1.020934947247522</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.312016422095238</v>
+        <v>2.34953605482393</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.319203387851814</v>
+        <v>-5.044584423412044</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8310573149379632</v>
+        <v>0.9409049007138712</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.083467668462009</v>
+        <v>-1.020934947247522</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.309014493315231</v>
+        <v>2.346534126043923</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.099182589814803</v>
+        <v>-4.824563625375033</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9206446711633816</v>
+        <v>1.03049225693929</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8797151021795415</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.395325437366633</v>
+        <v>2.432845070095325</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.899933959909994</v>
+        <v>-4.625314995470224</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.016238305927128</v>
+        <v>1.126085891703037</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8797151021795415</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.411219620168457</v>
+        <v>2.448739252897149</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.740418856390624</v>
+        <v>-4.465799891950854</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.081190191775178</v>
+        <v>1.191037777551087</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7827327198746589</v>
+        <v>-0.7201999986601716</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.50807452672038</v>
+        <v>2.545594159449073</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.595746711290887</v>
+        <v>-4.321127746851117</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.149147152376513</v>
+        <v>1.258994738152421</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6380605747749215</v>
+        <v>-0.5755278535604342</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.604965916341663</v>
+        <v>2.642485549070355</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.577977252359931</v>
+        <v>-4.303358287920161</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.071594628035617</v>
+        <v>1.181442213811525</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5577583946294786</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.530967283786957</v>
+        <v>2.56848691651565</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.491177754580922</v>
+        <v>-4.216558790141152</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.128714920469787</v>
+        <v>1.238562506245695</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5577583946294786</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.553367777109524</v>
+        <v>2.590887409838216</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.39148513985191</v>
+        <v>-4.11686617541214</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.168664367734804</v>
+        <v>1.278511953510712</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5205985011149541</v>
+        <v>-0.4580657799004669</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.613255747320343</v>
+        <v>2.650775380049035</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.45985532617592</v>
+        <v>-4.18523636173615</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.152323215679901</v>
+        <v>1.26217080145581</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.4487900808642519</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.629828089216774</v>
+        <v>2.667347721945466</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.338438896549444</v>
+        <v>-4.063819932109674</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.191326496162383</v>
+        <v>1.301174081938292</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.4487900808642519</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.620264797848665</v>
+        <v>2.657784430577358</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.369432055878149</v>
+        <v>-4.094813091438379</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.003638797471288</v>
+        <v>1.113486383247196</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.4487900808642519</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.444974362889052</v>
+        <v>2.482493995617745</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.193957796085679</v>
+        <v>-3.91933883164591</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.078395733380064</v>
+        <v>1.188243319155972</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.4487900808642519</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.44954159488084</v>
+        <v>2.487061227609532</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.482995180434443</v>
+        <v>3.830540313409439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.172118318326864</v>
+        <v>-4.030275084287158</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.087142998370388</v>
+        <v>1.14388029198627</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.4487900808642519</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.449553068767637</v>
+        <v>2.48707270149633</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.5%</t>
+          <t>-707.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.4%</t>
+          <t>782.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-564.6%</t>
+          <t>-587.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.2%</t>
+          <t>-277.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.8%</t>
+          <t>-271.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.9%</t>
+          <t>-275.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.3%</t>
+          <t>-201.1%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.457586628664018</v>
+        <v>-8.566067901468164</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2662289209567614</v>
+        <v>-0.3096214300784204</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.805329234088272</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.03396461436963</v>
+        <v>1.996444981640938</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.890935736774253</v>
+        <v>-8.9994170095784</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4435948687352589</v>
+        <v>-0.4869873778569174</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.805329234088272</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.029938309835227</v>
+        <v>1.992418677106535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.273937125516884</v>
+        <v>-9.382418398321031</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5968975255538953</v>
+        <v>-0.6402900346755538</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.805329234088272</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.029836208513643</v>
+        <v>1.992316575784951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.648922451688161</v>
+        <v>-9.757403724492308</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7443201400509758</v>
+        <v>-0.7877126491726347</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.18031456025955</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.807416528782307</v>
+        <v>1.769896896053614</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.00845277419216</v>
+        <v>-10.11693404699631</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8827819657545266</v>
+        <v>-0.9261744748761851</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.18031456025955</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.812766832080357</v>
+        <v>1.775247199351664</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.33485280285718</v>
+        <v>-10.44333407566132</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.005425957263354</v>
+        <v>-1.048818466385013</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.506714588924563</v>
+        <v>-2.56924731013905</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.624842834838526</v>
+        <v>1.587323202109834</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.55400177093137</v>
+        <v>-10.66248304373552</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.090043793871264</v>
+        <v>-1.133436302992923</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.72586355699876</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.496395204615777</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.55031084597496</v>
+        <v>-10.65879211877911</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.0885674238887</v>
+        <v>-1.131959933010358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.72586355699876</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.496395204615777</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.75456902130483</v>
+        <v>-10.86305029410897</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.164757496902003</v>
+        <v>-1.208150006023661</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.853502501612749</v>
+        <v>-2.916035222827236</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.425325034966026</v>
+        <v>1.387805402237333</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.972606792936</v>
+        <v>-11.08108806574015</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.247490051070038</v>
+        <v>-1.290882560191697</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.028273269708648</v>
+        <v>-3.090805990923135</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.324945128592923</v>
+        <v>1.28742549586423</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.89913696126855</v>
+        <v>-11.0076182340727</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.202730416909637</v>
+        <v>-1.246122926031296</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.954803438041199</v>
+        <v>-3.017336159255687</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.384398729086813</v>
+        <v>1.34687909635812</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.0742613786551</v>
+        <v>-11.18274265145924</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.258224963116738</v>
+        <v>-1.301617472238396</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.129927855427743</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.293879299402403</v>
+        <v>1.256359666673711</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.30871347266959</v>
+        <v>-11.41719474547373</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.35922496562413</v>
+        <v>-1.402617474745788</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.129927855427743</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.286660134500807</v>
+        <v>1.249140501772115</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.59651731720683</v>
+        <v>-11.70499859001097</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.481018694213001</v>
+        <v>-1.52441120333466</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.417731699964981</v>
+        <v>-3.480264421179469</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.107305637004488</v>
+        <v>1.069786004275796</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.82634176437065</v>
+        <v>-11.9348230371748</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.571832683239975</v>
+        <v>-1.615225192361634</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.580379237035142</v>
+        <v>-3.642911958249629</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.010832904600948</v>
+        <v>0.9733132718722559</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.05837068410691</v>
+        <v>-12.16685195691106</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.661950522505366</v>
+        <v>-1.705343031627024</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.642391934223565</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9763190149170087</v>
+        <v>0.9387993821883165</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.0063551701381</v>
+        <v>-12.11483644294225</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.637153981231439</v>
+        <v>-1.680546490353098</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.642391934223565</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9803093506034095</v>
+        <v>0.9427897178747173</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.14802701186222</v>
+        <v>-12.25650828466637</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.695297944819829</v>
+        <v>-1.738690453941488</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.642391934223565</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9788341237046678</v>
+        <v>0.9413144909759756</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2469337523215</v>
+        <v>-12.35541502512564</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.719807230838667</v>
+        <v>-1.763199739960326</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.74129867468284</v>
+        <v>-3.803831395897328</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9345434895939753</v>
+        <v>0.8970238568652826</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0477816450844</v>
+        <v>-12.15626291788854</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.65319752159051</v>
+        <v>-1.696590030712169</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.575976148733027</v>
+        <v>-3.638508869947514</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.02068587151718</v>
+        <v>0.9831662387884879</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.82193649236499</v>
+        <v>-11.93041776516913</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.553280387466538</v>
+        <v>-1.596672896588195</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.534049473145863</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.055420949905687</v>
+        <v>1.017901317176995</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.53566168004229</v>
+        <v>-11.64414295284644</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.4376313179814</v>
+        <v>-1.481023827103059</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.534049473145863</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.056560094461746</v>
+        <v>1.019040461733054</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.58855696808658</v>
+        <v>-11.69703824089072</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.456155659037008</v>
+        <v>-1.499548168158666</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.529094127057417</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.062167076276921</v>
+        <v>1.024647443548229</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.30464823715783</v>
+        <v>-11.41312950996197</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.336858462426871</v>
+        <v>-1.38025097154853</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.529094127057417</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.067900780515558</v>
+        <v>1.030381147786865</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.18922731301973</v>
+        <v>-11.29770858582388</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.300427355165498</v>
+        <v>-1.343819864287156</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.413673202919322</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.12741607260455</v>
+        <v>1.089896439875857</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.92539044581566</v>
+        <v>-11.03387171861981</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.204776089596778</v>
+        <v>-1.248168598718436</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.413673202919322</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.117532591291643</v>
+        <v>1.08001295856295</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.65814864494727</v>
+        <v>-10.76662991775141</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.099713929748793</v>
+        <v>-1.14310643887045</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.413673202919322</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.115698030792269</v>
+        <v>1.078178398063576</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.53484271646905</v>
+        <v>-10.64332398927319</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.050691873330966</v>
+        <v>-1.094084382452623</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.324255531791759</v>
+        <v>-3.386788253006246</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.169048318495346</v>
+        <v>1.131528685766653</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.51088917549309</v>
+        <v>-10.61937044829723</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.040441950795089</v>
+        <v>-1.083834459916747</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.300301990815801</v>
+        <v>-3.362834712030288</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.184088949226414</v>
+        <v>1.146569316497721</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.24682923717029</v>
+        <v>-10.35531050997444</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9480782916277226</v>
+        <v>-0.9914708007493802</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.036242052493005</v>
+        <v>-3.098774773707492</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.329264596058339</v>
+        <v>1.291744963329647</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.539749613665455</v>
+        <v>-9.6482308864696</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6680334758860882</v>
+        <v>-0.7114259850077462</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.036242052493005</v>
+        <v>-3.098774773707492</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.326477562398038</v>
+        <v>1.288957929669346</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.499565315299265</v>
+        <v>-9.608046588103409</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6516161326517707</v>
+        <v>-0.6950086417734287</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.996057754126814</v>
+        <v>-3.058590475341301</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.350931765305594</v>
+        <v>1.313412132576902</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.41949551976146</v>
+        <v>-9.527976792565605</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6202213932158922</v>
+        <v>-0.6636139023375502</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.91598795858901</v>
+        <v>-2.978520679803497</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.398340463849034</v>
+        <v>1.360820831120341</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.186014297531862</v>
+        <v>-9.294495570336007</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5189044754862007</v>
+        <v>-0.5622969846078587</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.682506736359411</v>
+        <v>-2.745039457573899</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.546353626024645</v>
+        <v>1.508833993295953</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.006305767387989</v>
+        <v>-9.114787040192134</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4499132737416103</v>
+        <v>-0.4933057828632683</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.625335232196715</v>
+        <v>-2.687867953411203</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.577764318209304</v>
+        <v>1.540244685480611</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.874030293757102</v>
+        <v>-8.982511566561246</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4016355975422283</v>
+        <v>-0.4450281066638864</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.493059758565829</v>
+        <v>-2.555592479780316</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.652497089134862</v>
+        <v>1.61497745640617</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.683430619083948</v>
+        <v>-8.791911891888093</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3225806669853304</v>
+        <v>-0.3659731761069884</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.302460083892676</v>
+        <v>-2.364992805107164</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.769671954626391</v>
+        <v>1.732152321897698</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.434430820400367</v>
+        <v>-8.542912093204512</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2100744062882391</v>
+        <v>-0.2534669154098972</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.302460083892676</v>
+        <v>-2.364992805107164</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.78257829585005</v>
+        <v>1.745058663121357</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.540020810173472</v>
+        <v>-8.648502082977616</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3802863317966998</v>
+        <v>-0.4236788409183578</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.408050073665781</v>
+        <v>-2.470582794880268</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.591248372386968</v>
+        <v>1.553728739658276</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.558755712292069</v>
+        <v>-8.667236985096213</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3392359507670522</v>
+        <v>-0.3826284598887102</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.408050073665781</v>
+        <v>-2.470582794880268</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.639792714264054</v>
+        <v>1.602273081535362</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.410815670884469</v>
+        <v>-8.519296943688614</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.39993885689218</v>
+        <v>-0.443331366013838</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.387729157757223</v>
+        <v>-2.45026187897171</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.532106341121022</v>
+        <v>1.494586708392329</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.283923264449399</v>
+        <v>-8.392404537253544</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3578958805716299</v>
+        <v>-0.401288389693288</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.260836751322153</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.599527798728585</v>
+        <v>1.562008165999893</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.240374857678708</v>
+        <v>-8.348856130482853</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3474371299584469</v>
+        <v>-0.3908296390801045</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.260836751322153</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.592567186633492</v>
+        <v>1.5550475539048</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.99822646422485</v>
+        <v>-8.106707737028994</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2361154181957605</v>
+        <v>-0.2795079273174181</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.260836751322153</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.607029541014635</v>
+        <v>1.569509908285943</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.934997092456501</v>
+        <v>-8.043478365260647</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2162915490292261</v>
+        <v>-0.2596840581508841</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.260836751322153</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.60156166147383</v>
+        <v>1.564042028745138</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.748509400079495</v>
+        <v>-7.856990672883641</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1441983780678466</v>
+        <v>-0.1875908871895051</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.074349058945147</v>
+        <v>-2.136881780159634</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.710952370910611</v>
+        <v>1.673432738181919</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.727360201176052</v>
+        <v>-7.835841473980198</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1280377202691443</v>
+        <v>-0.1714302293908023</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.053199860041703</v>
+        <v>-2.115732581256191</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.731342868490002</v>
+        <v>1.69382323576131</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.483594759192608</v>
+        <v>-7.592076031996753</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.0347508351287158</v>
+        <v>-0.07814334425037428</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.053199860041703</v>
+        <v>-2.115732581256191</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.727123576837053</v>
+        <v>1.689603944108361</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.219566691999347</v>
+        <v>-7.328047964803494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.07298470566860438</v>
+        <v>0.02959219654694589</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.85133446122575</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.850367130046641</v>
+        <v>1.812847497317949</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.969716298050272</v>
+        <v>-7.078197570854419</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1656669382319365</v>
+        <v>0.1222744291102775</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.85133446122575</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.843109205030343</v>
+        <v>1.805589572301651</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.666148809046294</v>
+        <v>-6.77463008185044</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2906930573541766</v>
+        <v>0.2473005482325181</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.85133446122575</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.846708328550992</v>
+        <v>1.8091886958223</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.59266890019428</v>
+        <v>-6.701150172998426</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.333412526949536</v>
+        <v>0.2900200178278771</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.777854552373735</v>
+        <v>-1.840387273588223</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.904123779916754</v>
+        <v>1.866604147188062</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.367635900525457</v>
+        <v>-6.476117173329603</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4224462044333621</v>
+        <v>0.3790536953117032</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.552821552704913</v>
+        <v>-1.6153542739194</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.038164057334345</v>
+        <v>2.000644424605652</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.15300152288905</v>
+        <v>-6.261482795693197</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5129947565422421</v>
+        <v>0.4696022474205832</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.338187175068506</v>
+        <v>-1.400719896282993</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.171639484970506</v>
+        <v>2.134119852241814</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886401165914698</v>
+        <v>-5.994882438718845</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6008291581157783</v>
+        <v>0.5574366489941198</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.338187175068506</v>
+        <v>-1.400719896282993</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.152833743754302</v>
+        <v>2.115314111025609</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645970669109838</v>
+        <v>-5.754451941913985</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6987444334626001</v>
+        <v>0.6553519243409411</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.097756678263646</v>
+        <v>-1.160289399478133</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.298835118462095</v>
+        <v>2.261315485733403</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.403179861460393</v>
+        <v>-5.511661134264539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7997900703571985</v>
+        <v>0.7563975612355396</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.097756678263646</v>
+        <v>-1.160289399478133</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.302764432296915</v>
+        <v>2.265244799568223</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.287240011835207</v>
+        <v>-5.395721284639354</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8468445941246125</v>
+        <v>0.8034520850029536</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.020934947247522</v>
+        <v>-1.083467668462009</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.34953605482393</v>
+        <v>2.312016422095238</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.044584423412044</v>
+        <v>-5.276698394197081</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9409049007138712</v>
+        <v>0.8480593123998563</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.020934947247522</v>
+        <v>-1.083467668462009</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.346534126043923</v>
+        <v>2.309014493315231</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.824563625375033</v>
+        <v>-5.05667759616007</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.03049225693929</v>
+        <v>0.9376466686252747</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8797151021795415</v>
+        <v>-0.9422478233940288</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.432845070095325</v>
+        <v>2.395325437366633</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.625314995470224</v>
+        <v>-4.857428966255261</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.126085891703037</v>
+        <v>1.033240303389022</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8797151021795415</v>
+        <v>-0.9422478233940288</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.448739252897149</v>
+        <v>2.411219620168457</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.465799891950854</v>
+        <v>-4.697913862735891</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.191037777551087</v>
+        <v>1.098192189237072</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7201999986601716</v>
+        <v>-0.7827327198746589</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.545594159449073</v>
+        <v>2.50807452672038</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.321127746851117</v>
+        <v>-4.553241717636154</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.258994738152421</v>
+        <v>1.166149149838406</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5755278535604342</v>
+        <v>-0.6380605747749215</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.642485549070355</v>
+        <v>2.604965916341663</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.303358287920161</v>
+        <v>-4.535472258705198</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.181442213811525</v>
+        <v>1.08859662549751</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5577583946294786</v>
+        <v>-0.6202911158439659</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.56848691651565</v>
+        <v>2.530967283786957</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.216558790141152</v>
+        <v>-4.44867276092619</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.238562506245695</v>
+        <v>1.14571691793168</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5577583946294786</v>
+        <v>-0.6202911158439659</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.590887409838216</v>
+        <v>2.553367777109524</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.11686617541214</v>
+        <v>-4.348980146197178</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.278511953510712</v>
+        <v>1.185666365196697</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4580657799004669</v>
+        <v>-0.5205985011149541</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.650775380049035</v>
+        <v>2.613255747320343</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.18523636173615</v>
+        <v>-4.417350332521188</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.26217080145581</v>
+        <v>1.169325213141795</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4487900808642519</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.667347721945466</v>
+        <v>2.629828089216774</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.063819932109674</v>
+        <v>-4.295933902894712</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.301174081938292</v>
+        <v>1.208328493624276</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4487900808642519</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.657784430577358</v>
+        <v>2.620264797848665</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.094813091438379</v>
+        <v>-4.326927062223417</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.113486383247196</v>
+        <v>1.020640794933181</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4487900808642519</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.482493995617745</v>
+        <v>2.444974362889052</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.91933883164591</v>
+        <v>-4.151452802430947</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.188243319155972</v>
+        <v>1.095397730841957</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4487900808642519</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.487061227609532</v>
+        <v>2.44954159488084</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.830540313409439</v>
+        <v>3.49266276288682</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.030275084287158</v>
+        <v>-4.262389055072196</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.14388029198627</v>
+        <v>1.051034703672255</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4487900808642519</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48707270149633</v>
+        <v>2.449553068767637</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>64.6%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>67.0%</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-25.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>136.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-707.4%</t>
+          <t>-696.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>782.4%</t>
+          <t>788.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.8%</t>
+          <t>-580.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.6%</t>
+          <t>-273.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-43.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.1%</t>
+          <t>-268.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-161.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.1%</t>
+          <t>-268.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.1%</t>
+          <t>-161.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1940"/>
+  <dimension ref="A1:G1941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.566067901468164</v>
+        <v>-8.453075280487655</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3096214300784204</v>
+        <v>-0.2644243816862164</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.801426887711112</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.996444981640938</v>
+        <v>2.036306022195926</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.9994170095784</v>
+        <v>-8.88642438859789</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4869873778569174</v>
+        <v>-0.4417903294647134</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.801426887711112</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.992418677106535</v>
+        <v>2.032279717661523</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.382418398321031</v>
+        <v>-9.269425777340521</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6402900346755538</v>
+        <v>-0.5950929862833498</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.801426887711112</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.992316575784951</v>
+        <v>2.032177616339939</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.757403724492308</v>
+        <v>-9.644411103511798</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7877126491726347</v>
+        <v>-0.7425156007804308</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.17641221388239</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.769896896053614</v>
+        <v>1.809757936608603</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.11693404699631</v>
+        <v>-10.0039414260158</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9261744748761851</v>
+        <v>-0.8809774264839811</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.17641221388239</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.775247199351664</v>
+        <v>1.815108239906653</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.44333407566132</v>
+        <v>-10.33034145468081</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.048818466385013</v>
+        <v>-1.003621417992809</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.56924731013905</v>
+        <v>-2.502812242547403</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.587323202109834</v>
+        <v>1.627184242664822</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.66248304373552</v>
+        <v>-10.54949042275501</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.133436302992923</v>
+        <v>-1.088239254600719</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.7219612106216</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.458875571887084</v>
+        <v>1.498736612442073</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.65879211877911</v>
+        <v>-10.5457994977986</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.131959933010358</v>
+        <v>-1.086762884618155</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.7219612106216</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.458875571887084</v>
+        <v>1.498736612442073</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.86305029410897</v>
+        <v>-10.75005767312846</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.208150006023661</v>
+        <v>-1.162952957631457</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.916035222827236</v>
+        <v>-2.849600155235589</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.387805402237333</v>
+        <v>1.427666442792322</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.08108806574015</v>
+        <v>-10.96809544475964</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.290882560191697</v>
+        <v>-1.245685511799493</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.090805990923135</v>
+        <v>-3.024370923331488</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.28742549586423</v>
+        <v>1.327286536419218</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.0076182340727</v>
+        <v>-10.89462561309219</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.246122926031296</v>
+        <v>-1.200925877639092</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.017336159255687</v>
+        <v>-2.950901091664039</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.34687909635812</v>
+        <v>1.386740136913109</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.18274265145924</v>
+        <v>-11.06975003047874</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.301617472238396</v>
+        <v>-1.256420423846192</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.126025509050583</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.256359666673711</v>
+        <v>1.296220707228699</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.41719474547373</v>
+        <v>-11.30420212449322</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.402617474745788</v>
+        <v>-1.357420426353584</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.126025509050583</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.249140501772115</v>
+        <v>1.289001542327103</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.70499859001097</v>
+        <v>-11.59200596903046</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.52441120333466</v>
+        <v>-1.479214154942456</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.480264421179469</v>
+        <v>-3.413829353587821</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.069786004275796</v>
+        <v>1.109647044830784</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.9348230371748</v>
+        <v>-11.82183041619429</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.615225192361634</v>
+        <v>-1.57002814396943</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.642911958249629</v>
+        <v>-3.576476890657982</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9733132718722559</v>
+        <v>1.013174312427244</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.16685195691106</v>
+        <v>-12.05385933593055</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.705343031627024</v>
+        <v>-1.66014598323482</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.638489587846405</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9387993821883165</v>
+        <v>0.9786604227433049</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.11483644294225</v>
+        <v>-12.00184382196174</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.680546490353098</v>
+        <v>-1.635349441960893</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.638489587846405</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9427897178747173</v>
+        <v>0.9826507584297057</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.25650828466637</v>
+        <v>-12.14351566368586</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.738690453941488</v>
+        <v>-1.693493405549284</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.638489587846405</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9413144909759756</v>
+        <v>0.981175531530964</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.35541502512564</v>
+        <v>-12.24242240414513</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.763199739960326</v>
+        <v>-1.718002691568122</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.803831395897328</v>
+        <v>-3.73739632830568</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8970238568652826</v>
+        <v>0.936884897420271</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.15626291788854</v>
+        <v>-12.04327029690803</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.696590030712169</v>
+        <v>-1.651392982319965</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.638508869947514</v>
+        <v>-3.572073802355867</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9831662387884879</v>
+        <v>1.023027279343476</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.93041776516913</v>
+        <v>-11.81742514418862</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.596672896588195</v>
+        <v>-1.551475848195991</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.530147126768703</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.017901317176995</v>
+        <v>1.057762357731983</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.64414295284644</v>
+        <v>-11.53115033186593</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.481023827103059</v>
+        <v>-1.435826778710855</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.530147126768703</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.019040461733054</v>
+        <v>1.058901502288042</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.69703824089072</v>
+        <v>-11.58404561991021</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.499548168158666</v>
+        <v>-1.454351119766462</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.525191780680257</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.024647443548229</v>
+        <v>1.064508484103217</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.41312950996197</v>
+        <v>-11.30013688898146</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.38025097154853</v>
+        <v>-1.335053923156326</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.525191780680257</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.030381147786865</v>
+        <v>1.070242188341854</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.29770858582388</v>
+        <v>-11.18471596484337</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.343819864287156</v>
+        <v>-1.298622815894952</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.409770856542162</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.089896439875857</v>
+        <v>1.129757480430846</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.03387171861981</v>
+        <v>-10.9208790976393</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.248168598718436</v>
+        <v>-1.202971550326232</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.409770856542162</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08001295856295</v>
+        <v>1.119873999117938</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.76662991775141</v>
+        <v>-10.6536372967709</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.14310643887045</v>
+        <v>-1.097909390478246</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.409770856542162</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.078178398063576</v>
+        <v>1.118039438618565</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64332398927319</v>
+        <v>-10.53033136829268</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.094084382452623</v>
+        <v>-1.048887334060419</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.386788253006246</v>
+        <v>-3.320353185414599</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.131528685766653</v>
+        <v>1.171389726321642</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61937044829723</v>
+        <v>-10.50637782731672</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083834459916747</v>
+        <v>-1.038637411524543</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.362834712030288</v>
+        <v>-3.296399644438641</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.146569316497721</v>
+        <v>1.18643035705271</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35531050997444</v>
+        <v>-10.24231788899393</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9914708007493802</v>
+        <v>-0.9462737523571763</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.098774773707492</v>
+        <v>-3.032339706115845</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.291744963329647</v>
+        <v>1.331606003884635</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.6482308864696</v>
+        <v>-9.701375957124718</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7114259850077462</v>
+        <v>-0.7326840132697936</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.098774773707492</v>
+        <v>-3.032339706115845</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.288957929669346</v>
+        <v>1.328818970224334</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.608046588103409</v>
+        <v>-9.661191658758527</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6950086417734287</v>
+        <v>-0.7162666700354761</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.058590475341301</v>
+        <v>-2.992155407749654</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.313412132576902</v>
+        <v>1.35327317313189</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.527976792565605</v>
+        <v>-9.581121863220723</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6636139023375502</v>
+        <v>-0.6848719305995972</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.978520679803497</v>
+        <v>-2.91208561221185</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.360820831120341</v>
+        <v>1.40068187167533</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.294495570336007</v>
+        <v>-9.347640640991123</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5622969846078587</v>
+        <v>-0.5835550128699052</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.745039457573899</v>
+        <v>-2.678604389982251</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.508833993295953</v>
+        <v>1.548695033850941</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.114787040192134</v>
+        <v>-9.16793211084725</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4933057828632683</v>
+        <v>-0.5145638111253148</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.687867953411203</v>
+        <v>-2.621432885819555</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.540244685480611</v>
+        <v>1.5801057260356</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.982511566561246</v>
+        <v>-9.035656637216363</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4450281066638864</v>
+        <v>-0.4662861349259328</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.555592479780316</v>
+        <v>-2.489157412188669</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.61497745640617</v>
+        <v>1.654838496961158</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.791911891888093</v>
+        <v>-8.845056962543209</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3659731761069884</v>
+        <v>-0.3872312043690349</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.298557737515516</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.732152321897698</v>
+        <v>1.772013362452687</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.542912093204512</v>
+        <v>-8.596057163859628</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2534669154098972</v>
+        <v>-0.2747249436719437</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.298557737515516</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.745058663121357</v>
+        <v>1.784919703676345</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.648502082977616</v>
+        <v>-8.701647153632733</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4236788409183578</v>
+        <v>-0.4449368691804043</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.404147727288621</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.553728739658276</v>
+        <v>1.593589780213264</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.667236985096213</v>
+        <v>-8.72038205575133</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3826284598887102</v>
+        <v>-0.4038864881507567</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.404147727288621</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.602273081535362</v>
+        <v>1.64213412209035</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.519296943688614</v>
+        <v>-8.57244201434373</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.443331366013838</v>
+        <v>-0.4645893942758845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.45026187897171</v>
+        <v>-2.383826811380063</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.494586708392329</v>
+        <v>1.534447748947317</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.392404537253544</v>
+        <v>-8.44554960790866</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.401288389693288</v>
+        <v>-0.4225464179553344</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.256934404944993</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.562008165999893</v>
+        <v>1.601869206554881</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.348856130482853</v>
+        <v>-8.402001201137969</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3908296390801045</v>
+        <v>-0.412087667342151</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.256934404944993</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.5550475539048</v>
+        <v>1.594908594459788</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.106707737028994</v>
+        <v>-8.159852807684111</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2795079273174181</v>
+        <v>-0.3007659555794646</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.256934404944993</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.569509908285943</v>
+        <v>1.609370948840931</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.043478365260647</v>
+        <v>-8.096623435915763</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2596840581508841</v>
+        <v>-0.2809420864129306</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.256934404944993</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.564042028745138</v>
+        <v>1.603903069300126</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.856990672883641</v>
+        <v>-7.910135743538757</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1875908871895051</v>
+        <v>-0.2088489154515516</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.136881780159634</v>
+        <v>-2.070446712567987</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.673432738181919</v>
+        <v>1.713293778736907</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.835841473980198</v>
+        <v>-7.888986544635314</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1714302293908023</v>
+        <v>-0.1926882576528488</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.049297513664543</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.69382323576131</v>
+        <v>1.733684276316298</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.592076031996753</v>
+        <v>-7.645221102651869</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07814334425037428</v>
+        <v>-0.09940137251242076</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.049297513664543</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.689603944108361</v>
+        <v>1.729464984663349</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.328047964803494</v>
+        <v>-7.38119303545861</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.02959219654694589</v>
+        <v>0.008334168284899413</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.84743211484859</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.812847497317949</v>
+        <v>1.852708537872937</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.078197570854419</v>
+        <v>-7.131342641509535</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1222744291102775</v>
+        <v>0.101016400848231</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.84743211484859</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.805589572301651</v>
+        <v>1.845450612856639</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.77463008185044</v>
+        <v>-6.827775152505557</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2473005482325181</v>
+        <v>0.2260425199704716</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.84743211484859</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.8091886958223</v>
+        <v>1.849049736377288</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.701150172998426</v>
+        <v>-6.754295243653543</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2900200178278771</v>
+        <v>0.2687619895658306</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.840387273588223</v>
+        <v>-1.773952205996576</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.866604147188062</v>
+        <v>1.90646518774305</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.476117173329603</v>
+        <v>-6.52926224398472</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3790536953117032</v>
+        <v>0.3577956670496567</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.6153542739194</v>
+        <v>-1.548919206327753</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.000644424605652</v>
+        <v>2.040505465160641</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.261482795693197</v>
+        <v>-6.314627866348313</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4696022474205832</v>
+        <v>0.4483442191585367</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.334284828691346</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.134119852241814</v>
+        <v>2.173980892796802</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.994882438718845</v>
+        <v>-6.048027509373961</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5574366489941198</v>
+        <v>0.5361786207320733</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.334284828691346</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.115314111025609</v>
+        <v>2.155175151580598</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.754451941913985</v>
+        <v>-5.807597012569101</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6553519243409411</v>
+        <v>0.6340938960788947</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.093854331886486</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.261315485733403</v>
+        <v>2.301176526288391</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.511661134264539</v>
+        <v>-5.564806204919655</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7563975612355396</v>
+        <v>0.7351395329734931</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.093854331886486</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.265244799568223</v>
+        <v>2.305105840123212</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.395721284639354</v>
+        <v>-5.44886635529447</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8034520850029536</v>
+        <v>0.7821940567409071</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.083467668462009</v>
+        <v>-1.017032600870362</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.312016422095238</v>
+        <v>2.351877462650226</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.276698394197081</v>
+        <v>-5.206210766871306</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8480593123998563</v>
+        <v>0.8762543633301663</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.083467668462009</v>
+        <v>-1.017032600870362</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.309014493315231</v>
+        <v>2.348875533870219</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.05667759616007</v>
+        <v>-4.986189968834296</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9376466686252747</v>
+        <v>0.9658417195555846</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8758127558023816</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.395325437366633</v>
+        <v>2.435186477921622</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.857428966255261</v>
+        <v>-4.786941338929487</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.033240303389022</v>
+        <v>1.061435354319332</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8758127558023816</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.411219620168457</v>
+        <v>2.451080660723445</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.697913862735891</v>
+        <v>-4.627426235410117</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.098192189237072</v>
+        <v>1.126387240167381</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7827327198746589</v>
+        <v>-0.7162976522830117</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.50807452672038</v>
+        <v>2.547935567275369</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.553241717636154</v>
+        <v>-4.48275409031038</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.166149149838406</v>
+        <v>1.194344200768716</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6380605747749215</v>
+        <v>-0.5716255071832743</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.604965916341663</v>
+        <v>2.644826956896651</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.535472258705198</v>
+        <v>-4.464984631379424</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.08859662549751</v>
+        <v>1.11679167642782</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5538560482523187</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.530967283786957</v>
+        <v>2.570828324341946</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.44867276092619</v>
+        <v>-4.378185133600415</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.14571691793168</v>
+        <v>1.17391196886199</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5538560482523187</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.553367777109524</v>
+        <v>2.593228817664512</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.348980146197178</v>
+        <v>-4.278492518871403</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.185666365196697</v>
+        <v>1.213861416127007</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5205985011149541</v>
+        <v>-0.454163433523307</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.613255747320343</v>
+        <v>2.653116787875331</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.417350332521188</v>
+        <v>-4.346862705195413</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.169325213141795</v>
+        <v>1.197520264072105</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.444887734487092</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.629828089216774</v>
+        <v>2.669689129771762</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.295933902894712</v>
+        <v>-4.225446275568936</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.208328493624276</v>
+        <v>1.236523544554587</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.444887734487092</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.620264797848665</v>
+        <v>2.660125838403653</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.326927062223417</v>
+        <v>-4.256439434897642</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.020640794933181</v>
+        <v>1.048835845863491</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.444887734487092</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.444974362889052</v>
+        <v>2.48483540344404</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.151452802430947</v>
+        <v>-4.080965175105172</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.095397730841957</v>
+        <v>1.123592781772267</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.444887734487092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.44954159488084</v>
+        <v>2.489402635435828</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,45 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.49266276288682</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.262389055072196</v>
+        <v>-4.191901427746421</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.051034703672255</v>
+        <v>1.079229754602565</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.444887734487092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.449553068767637</v>
+        <v>2.489414109322626</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="2" t="n">
+        <v>45403</v>
+      </c>
+      <c r="B1941" t="n">
+        <v>3.829319801815581</v>
+      </c>
+      <c r="C1941" t="n">
+        <v>2.857013232169131</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>-4.191901427746421</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>1.079229754602565</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>-0.444887734487092</v>
+      </c>
+      <c r="G1941" t="n">
+        <v>2.850077029155499</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-51.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.4%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.1%</t>
+          <t>-707.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.1%</t>
+          <t>782.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-580.8%</t>
+          <t>-587.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.0%</t>
+          <t>-277.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-43.5%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-268.3%</t>
+          <t>-271.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.5%</t>
+          <t>-275.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-161.0%</t>
+          <t>-186.7%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.453075280487655</v>
+        <v>-8.566067901468164</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2644243816862164</v>
+        <v>-0.3096214300784204</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.801426887711112</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.036306022195926</v>
+        <v>1.996444981640938</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.88642438859789</v>
+        <v>-8.9994170095784</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4417903294647134</v>
+        <v>-0.4869873778569174</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.801426887711112</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.032279717661523</v>
+        <v>1.992418677106535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.269425777340521</v>
+        <v>-9.382418398321031</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5950929862833498</v>
+        <v>-0.6402900346755538</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.801426887711112</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.032177616339939</v>
+        <v>1.992316575784951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.644411103511798</v>
+        <v>-9.757403724492308</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7425156007804308</v>
+        <v>-0.7877126491726347</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.17641221388239</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.809757936608603</v>
+        <v>1.769896896053614</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.0039414260158</v>
+        <v>-10.11693404699631</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8809774264839811</v>
+        <v>-0.9261744748761851</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.17641221388239</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.815108239906653</v>
+        <v>1.775247199351664</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.33034145468081</v>
+        <v>-10.44333407566132</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.003621417992809</v>
+        <v>-1.048818466385013</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.502812242547403</v>
+        <v>-2.56924731013905</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.627184242664822</v>
+        <v>1.587323202109834</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.54949042275501</v>
+        <v>-10.66248304373552</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.088239254600719</v>
+        <v>-1.133436302992923</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.7219612106216</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.498736612442073</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.5457994977986</v>
+        <v>-10.65879211877911</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.086762884618155</v>
+        <v>-1.131959933010358</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.7219612106216</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.498736612442073</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.75005767312846</v>
+        <v>-10.86305029410897</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.162952957631457</v>
+        <v>-1.208150006023661</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.849600155235589</v>
+        <v>-2.916035222827236</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.427666442792322</v>
+        <v>1.387805402237333</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.96809544475964</v>
+        <v>-11.08108806574015</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.245685511799493</v>
+        <v>-1.290882560191697</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.024370923331488</v>
+        <v>-3.090805990923135</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.327286536419218</v>
+        <v>1.28742549586423</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.89462561309219</v>
+        <v>-11.0076182340727</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.200925877639092</v>
+        <v>-1.246122926031296</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.950901091664039</v>
+        <v>-3.017336159255687</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.386740136913109</v>
+        <v>1.34687909635812</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.06975003047874</v>
+        <v>-11.18274265145924</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.256420423846192</v>
+        <v>-1.301617472238396</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.126025509050583</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.296220707228699</v>
+        <v>1.256359666673711</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.30420212449322</v>
+        <v>-11.41719474547373</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.357420426353584</v>
+        <v>-1.402617474745788</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.126025509050583</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.289001542327103</v>
+        <v>1.249140501772115</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.59200596903046</v>
+        <v>-11.70499859001097</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.479214154942456</v>
+        <v>-1.52441120333466</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.413829353587821</v>
+        <v>-3.480264421179469</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.109647044830784</v>
+        <v>1.069786004275796</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.82183041619429</v>
+        <v>-11.9348230371748</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.57002814396943</v>
+        <v>-1.615225192361634</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.576476890657982</v>
+        <v>-3.642911958249629</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.013174312427244</v>
+        <v>0.9733132718722559</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.05385933593055</v>
+        <v>-12.16685195691106</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.66014598323482</v>
+        <v>-1.705343031627024</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.638489587846405</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9786604227433049</v>
+        <v>0.9387993821883165</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.00184382196174</v>
+        <v>-12.11483644294225</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.635349441960893</v>
+        <v>-1.680546490353098</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.638489587846405</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9826507584297057</v>
+        <v>0.9427897178747173</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.14351566368586</v>
+        <v>-12.25650828466637</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.693493405549284</v>
+        <v>-1.738690453941488</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.638489587846405</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.981175531530964</v>
+        <v>0.9413144909759756</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.24242240414513</v>
+        <v>-12.35541502512564</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.718002691568122</v>
+        <v>-1.763199739960326</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.73739632830568</v>
+        <v>-3.803831395897328</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.936884897420271</v>
+        <v>0.8970238568652826</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.04327029690803</v>
+        <v>-12.15626291788854</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.651392982319965</v>
+        <v>-1.696590030712169</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.572073802355867</v>
+        <v>-3.638508869947514</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.023027279343476</v>
+        <v>0.9831662387884879</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.81742514418862</v>
+        <v>-11.93041776516913</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.551475848195991</v>
+        <v>-1.596672896588195</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.530147126768703</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.057762357731983</v>
+        <v>1.017901317176995</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.53115033186593</v>
+        <v>-11.64414295284644</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.435826778710855</v>
+        <v>-1.481023827103059</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.530147126768703</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.058901502288042</v>
+        <v>1.019040461733054</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.58404561991021</v>
+        <v>-11.69703824089072</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.454351119766462</v>
+        <v>-1.499548168158666</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.525191780680257</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.064508484103217</v>
+        <v>1.024647443548229</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.30013688898146</v>
+        <v>-11.41312950996197</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.335053923156326</v>
+        <v>-1.38025097154853</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.525191780680257</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.070242188341854</v>
+        <v>1.030381147786865</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.18471596484337</v>
+        <v>-11.29770858582388</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.298622815894952</v>
+        <v>-1.343819864287156</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.409770856542162</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.129757480430846</v>
+        <v>1.089896439875857</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9208790976393</v>
+        <v>-11.03387171861981</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.202971550326232</v>
+        <v>-1.248168598718436</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.409770856542162</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.119873999117938</v>
+        <v>1.08001295856295</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6536372967709</v>
+        <v>-10.76662991775141</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.097909390478246</v>
+        <v>-1.14310643887045</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.409770856542162</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.118039438618565</v>
+        <v>1.078178398063576</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.53033136829268</v>
+        <v>-10.64332398927319</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.048887334060419</v>
+        <v>-1.094084382452623</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.320353185414599</v>
+        <v>-3.386788253006246</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.171389726321642</v>
+        <v>1.131528685766653</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.50637782731672</v>
+        <v>-10.61937044829723</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.038637411524543</v>
+        <v>-1.083834459916747</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.296399644438641</v>
+        <v>-3.362834712030288</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.18643035705271</v>
+        <v>1.146569316497721</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.24231788899393</v>
+        <v>-10.35531050997444</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9462737523571763</v>
+        <v>-0.9914708007493802</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.032339706115845</v>
+        <v>-3.098774773707492</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.331606003884635</v>
+        <v>1.291744963329647</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.701375957124718</v>
+        <v>-9.6482308864696</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7326840132697936</v>
+        <v>-0.7114259850077462</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.032339706115845</v>
+        <v>-3.098774773707492</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.328818970224334</v>
+        <v>1.288957929669346</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.661191658758527</v>
+        <v>-9.608046588103409</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7162666700354761</v>
+        <v>-0.6950086417734287</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.992155407749654</v>
+        <v>-3.058590475341301</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.35327317313189</v>
+        <v>1.313412132576902</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.581121863220723</v>
+        <v>-9.527976792565605</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6848719305995972</v>
+        <v>-0.6636139023375502</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.91208561221185</v>
+        <v>-2.978520679803497</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.40068187167533</v>
+        <v>1.360820831120341</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.347640640991123</v>
+        <v>-9.294495570336007</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5835550128699052</v>
+        <v>-0.5622969846078587</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.678604389982251</v>
+        <v>-2.745039457573899</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.548695033850941</v>
+        <v>1.508833993295953</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.16793211084725</v>
+        <v>-9.114787040192134</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5145638111253148</v>
+        <v>-0.4933057828632683</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.621432885819555</v>
+        <v>-2.687867953411203</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.5801057260356</v>
+        <v>1.540244685480611</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.035656637216363</v>
+        <v>-8.982511566561246</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4662861349259328</v>
+        <v>-0.4450281066638864</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.489157412188669</v>
+        <v>-2.555592479780316</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.654838496961158</v>
+        <v>1.61497745640617</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.845056962543209</v>
+        <v>-8.791911891888093</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3872312043690349</v>
+        <v>-0.3659731761069884</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.298557737515516</v>
+        <v>-2.364992805107164</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.772013362452687</v>
+        <v>1.732152321897698</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.596057163859628</v>
+        <v>-8.542912093204512</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2747249436719437</v>
+        <v>-0.2534669154098972</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.298557737515516</v>
+        <v>-2.364992805107164</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.784919703676345</v>
+        <v>1.745058663121357</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.701647153632733</v>
+        <v>-8.648502082977616</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4449368691804043</v>
+        <v>-0.4236788409183578</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.404147727288621</v>
+        <v>-2.470582794880268</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.593589780213264</v>
+        <v>1.553728739658276</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.72038205575133</v>
+        <v>-8.667236985096213</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4038864881507567</v>
+        <v>-0.3826284598887102</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.404147727288621</v>
+        <v>-2.470582794880268</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.64213412209035</v>
+        <v>1.602273081535362</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.57244201434373</v>
+        <v>-8.519296943688614</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4645893942758845</v>
+        <v>-0.443331366013838</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.383826811380063</v>
+        <v>-2.45026187897171</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.534447748947317</v>
+        <v>1.494586708392329</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.44554960790866</v>
+        <v>-8.392404537253544</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4225464179553344</v>
+        <v>-0.401288389693288</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.256934404944993</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.601869206554881</v>
+        <v>1.562008165999893</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.402001201137969</v>
+        <v>-8.348856130482853</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.412087667342151</v>
+        <v>-0.3908296390801045</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.256934404944993</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.594908594459788</v>
+        <v>1.5550475539048</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.159852807684111</v>
+        <v>-8.106707737028994</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3007659555794646</v>
+        <v>-0.2795079273174181</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.256934404944993</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.609370948840931</v>
+        <v>1.569509908285943</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.096623435915763</v>
+        <v>-8.043478365260647</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2809420864129306</v>
+        <v>-0.2596840581508841</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.256934404944993</v>
+        <v>-2.323369472536641</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.603903069300126</v>
+        <v>1.564042028745138</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.910135743538757</v>
+        <v>-7.856990672883641</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2088489154515516</v>
+        <v>-0.1875908871895051</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.070446712567987</v>
+        <v>-2.136881780159634</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.713293778736907</v>
+        <v>1.673432738181919</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.888986544635314</v>
+        <v>-7.835841473980198</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1926882576528488</v>
+        <v>-0.1714302293908023</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.049297513664543</v>
+        <v>-2.115732581256191</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.733684276316298</v>
+        <v>1.69382323576131</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.645221102651869</v>
+        <v>-7.592076031996753</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.09940137251242076</v>
+        <v>-0.07814334425037428</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.049297513664543</v>
+        <v>-2.115732581256191</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.729464984663349</v>
+        <v>1.689603944108361</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.38119303545861</v>
+        <v>-7.328047964803494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.008334168284899413</v>
+        <v>0.02959219654694589</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.84743211484859</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.852708537872937</v>
+        <v>1.812847497317949</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.131342641509535</v>
+        <v>-7.078197570854419</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.101016400848231</v>
+        <v>0.1222744291102775</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.84743211484859</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.845450612856639</v>
+        <v>1.805589572301651</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.827775152505557</v>
+        <v>-6.77463008185044</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2260425199704716</v>
+        <v>0.2473005482325181</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.84743211484859</v>
+        <v>-1.913867182440237</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.849049736377288</v>
+        <v>1.8091886958223</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.754295243653543</v>
+        <v>-6.701150172998426</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2687619895658306</v>
+        <v>0.2900200178278771</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.773952205996576</v>
+        <v>-1.840387273588223</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.90646518774305</v>
+        <v>1.866604147188062</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.52926224398472</v>
+        <v>-6.476117173329603</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3577956670496567</v>
+        <v>0.3790536953117032</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.548919206327753</v>
+        <v>-1.6153542739194</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.040505465160641</v>
+        <v>2.000644424605652</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.314627866348313</v>
+        <v>-6.261482795693197</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4483442191585367</v>
+        <v>0.4696022474205832</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.334284828691346</v>
+        <v>-1.400719896282993</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.173980892796802</v>
+        <v>2.134119852241814</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.048027509373961</v>
+        <v>-5.994882438718845</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5361786207320733</v>
+        <v>0.5574366489941198</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.334284828691346</v>
+        <v>-1.400719896282993</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.155175151580598</v>
+        <v>2.115314111025609</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.807597012569101</v>
+        <v>-5.754451941913985</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6340938960788947</v>
+        <v>0.6553519243409411</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.093854331886486</v>
+        <v>-1.160289399478133</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.301176526288391</v>
+        <v>2.261315485733403</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.564806204919655</v>
+        <v>-5.511661134264539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7351395329734931</v>
+        <v>0.7563975612355396</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.093854331886486</v>
+        <v>-1.160289399478133</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.305105840123212</v>
+        <v>2.265244799568223</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.44886635529447</v>
+        <v>-5.395721284639354</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7821940567409071</v>
+        <v>0.8034520850029536</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.017032600870362</v>
+        <v>-1.083467668462009</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.351877462650226</v>
+        <v>2.312016422095238</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.206210766871306</v>
+        <v>-5.276698394197081</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8762543633301663</v>
+        <v>0.8480593123998563</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.017032600870362</v>
+        <v>-1.083467668462009</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.348875533870219</v>
+        <v>2.309014493315231</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.986189968834296</v>
+        <v>-5.05667759616007</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9658417195555846</v>
+        <v>0.9376466686252747</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8758127558023816</v>
+        <v>-0.9422478233940288</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.435186477921622</v>
+        <v>2.395325437366633</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.786941338929487</v>
+        <v>-4.857428966255261</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.061435354319332</v>
+        <v>1.033240303389022</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8758127558023816</v>
+        <v>-0.9422478233940288</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.451080660723445</v>
+        <v>2.411219620168457</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.627426235410117</v>
+        <v>-4.697913862735891</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.126387240167381</v>
+        <v>1.098192189237072</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7162976522830117</v>
+        <v>-0.7827327198746589</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.547935567275369</v>
+        <v>2.50807452672038</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.48275409031038</v>
+        <v>-4.553241717636154</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.194344200768716</v>
+        <v>1.166149149838406</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5716255071832743</v>
+        <v>-0.6380605747749215</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.644826956896651</v>
+        <v>2.604965916341663</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.464984631379424</v>
+        <v>-4.535472258705198</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.11679167642782</v>
+        <v>1.08859662549751</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5538560482523187</v>
+        <v>-0.6202911158439659</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.570828324341946</v>
+        <v>2.530967283786957</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.378185133600415</v>
+        <v>-4.44867276092619</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.17391196886199</v>
+        <v>1.14571691793168</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5538560482523187</v>
+        <v>-0.6202911158439659</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.593228817664512</v>
+        <v>2.553367777109524</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.278492518871403</v>
+        <v>-4.348980146197178</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.213861416127007</v>
+        <v>1.185666365196697</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.454163433523307</v>
+        <v>-0.5205985011149541</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.653116787875331</v>
+        <v>2.613255747320343</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.346862705195413</v>
+        <v>-4.417350332521188</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.197520264072105</v>
+        <v>1.169325213141795</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.669689129771762</v>
+        <v>2.629828089216774</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.225446275568936</v>
+        <v>-4.295933902894712</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.236523544554587</v>
+        <v>1.208328493624276</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.660125838403653</v>
+        <v>2.620264797848665</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.256439434897642</v>
+        <v>-4.326927062223417</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.048835845863491</v>
+        <v>1.020640794933181</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.48483540344404</v>
+        <v>2.444974362889052</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.080965175105172</v>
+        <v>-4.151452802430947</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.123592781772267</v>
+        <v>1.095397730841957</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.489402635435828</v>
+        <v>2.44954159488084</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.191901427746421</v>
+        <v>-4.262389055072196</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.079229754602565</v>
+        <v>1.051034703672255</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.489414109322626</v>
+        <v>2.449553068767637</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.829319801815581</v>
+        <v>3.497736301981837</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.857013232169131</v>
+        <v>2.599966272786478</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.191901427746421</v>
+        <v>-4.262389055072196</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.079229754602565</v>
+        <v>1.051034703672255</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.444887734487092</v>
+        <v>-0.5113228020787391</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.850077029155499</v>
+        <v>2.593030069772846</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>134.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-707.4%</t>
+          <t>-681.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>782.6%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.8%</t>
+          <t>-549.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.6%</t>
+          <t>-268.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.1%</t>
+          <t>-255.8%</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-161.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,27 +1476,27 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.7%</t>
+          <t>-145.0%</t>
         </is>
       </c>
     </row>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.9994170095784</v>
+        <v>-8.739581339122513</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4869873778569174</v>
+        <v>-0.3830531096745626</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.382418398321031</v>
+        <v>-9.122582727865144</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6402900346755538</v>
+        <v>-0.536355766493199</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.757403724492308</v>
+        <v>-9.497568054036421</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7877126491726347</v>
+        <v>-0.68377838099028</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.242847281474037</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.11693404699631</v>
+        <v>-9.857098376540423</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9261744748761851</v>
+        <v>-0.8222402066938304</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.242847281474037</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.44333407566132</v>
+        <v>-10.18349840520544</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.048818466385013</v>
+        <v>-0.9448841982026583</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.56924731013905</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.66248304373552</v>
+        <v>-10.40264737327963</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.133436302992923</v>
+        <v>-1.029502034810568</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.788396278213247</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.65879211877911</v>
+        <v>-10.39895644832322</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.131959933010358</v>
+        <v>-1.028025664828004</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.788396278213247</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.86305029410897</v>
+        <v>-10.60321462365309</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.208150006023661</v>
+        <v>-1.104215737841307</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.916035222827236</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.08108806574015</v>
+        <v>-10.82125239528426</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.290882560191697</v>
+        <v>-1.186948292009342</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.090805990923135</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.0076182340727</v>
+        <v>-10.74778256361681</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.246122926031296</v>
+        <v>-1.142188657848942</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.017336159255687</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.18274265145924</v>
+        <v>-10.92290698100336</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.301617472238396</v>
+        <v>-1.197683204056042</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.19246057664223</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.41719474547373</v>
+        <v>-11.15735907501785</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.402617474745788</v>
+        <v>-1.298683206563434</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.19246057664223</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.70499859001097</v>
+        <v>-11.44516291955509</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.52441120333466</v>
+        <v>-1.420476935152305</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.480264421179469</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.9348230371748</v>
+        <v>-11.67498736671891</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.615225192361634</v>
+        <v>-1.511290924179279</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.642911958249629</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.16685195691106</v>
+        <v>-11.90701628645517</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.705343031627024</v>
+        <v>-1.601408763444669</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.704924655438052</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.11483644294225</v>
+        <v>-11.85500077248636</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.680546490353098</v>
+        <v>-1.576612222170743</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.704924655438052</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.25650828466637</v>
+        <v>-11.99667261421048</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.738690453941488</v>
+        <v>-1.634756185759133</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.704924655438052</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.35541502512564</v>
+        <v>-12.09557935466976</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.763199739960326</v>
+        <v>-1.65926547177797</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.803831395897328</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.15626291788854</v>
+        <v>-11.89642724743266</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.696590030712169</v>
+        <v>-1.592655762529814</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.638508869947514</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.93041776516913</v>
+        <v>-11.67058209471325</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.596672896588195</v>
+        <v>-1.492738628405842</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.596582194360351</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.64414295284644</v>
+        <v>-11.38430728239055</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.481023827103059</v>
+        <v>-1.377089558920705</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.596582194360351</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.69703824089072</v>
+        <v>-11.43720257043484</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.499548168158666</v>
+        <v>-1.395613899976311</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.591626848271904</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.41312950996197</v>
+        <v>-11.15329383950609</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.38025097154853</v>
+        <v>-1.276316703366176</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.591626848271904</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.29770858582388</v>
+        <v>-11.03787291536799</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.343819864287156</v>
+        <v>-1.239885596104802</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.476205924133809</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.03387171861981</v>
+        <v>-10.77403604816392</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.248168598718436</v>
+        <v>-1.144234330536082</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.76662991775141</v>
+        <v>-10.50679424729553</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.14310643887045</v>
+        <v>-1.039172170688097</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64332398927319</v>
+        <v>-10.38348831881731</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.094084382452623</v>
+        <v>-0.99015011427027</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.386788253006246</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61937044829723</v>
+        <v>-10.35953477784135</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083834459916747</v>
+        <v>-0.979900191734393</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.362834712030288</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35531050997444</v>
+        <v>-10.09547483951855</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9914708007493802</v>
+        <v>-0.8875365325670259</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.098774773707492</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.6482308864696</v>
+        <v>-9.388395216013715</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7114259850077462</v>
+        <v>-0.6074917168253924</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.608046588103409</v>
+        <v>-9.348210917647524</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6950086417734287</v>
+        <v>-0.5910743735910748</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.527976792565605</v>
+        <v>-9.26814112210972</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6636139023375502</v>
+        <v>-0.5596796341551959</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.294495570336007</v>
+        <v>-9.034659899880122</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5622969846078587</v>
+        <v>-0.4583627164255044</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.114787040192134</v>
+        <v>-8.854951369736249</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4933057828632683</v>
+        <v>-0.3893715146809145</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.982511566561246</v>
+        <v>-8.722675896105361</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4450281066638864</v>
+        <v>-0.3410938384815325</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.791911891888093</v>
+        <v>-8.532076221432208</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3659731761069884</v>
+        <v>-0.2620389079246341</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.542912093204512</v>
+        <v>-8.283076422748627</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2534669154098972</v>
+        <v>-0.1495326472275429</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.648502082977616</v>
+        <v>-8.388666412521731</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4236788409183578</v>
+        <v>-0.3197445727360035</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.667236985096213</v>
+        <v>-8.407401314640328</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3826284598887102</v>
+        <v>-0.2786941917063559</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.519296943688614</v>
+        <v>-8.259461273232729</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.443331366013838</v>
+        <v>-0.3393970978314838</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.392404537253544</v>
+        <v>-8.132568866797659</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.401288389693288</v>
+        <v>-0.2973541215109341</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.348856130482853</v>
+        <v>-8.089020460026967</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3908296390801045</v>
+        <v>-0.2868953708977506</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.106707737028994</v>
+        <v>-7.846872066573109</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2795079273174181</v>
+        <v>-0.1755736591350643</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.043478365260647</v>
+        <v>-7.783642694804761</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2596840581508841</v>
+        <v>-0.1557497899685298</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.856990672883641</v>
+        <v>-7.597155002427755</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1875908871895051</v>
+        <v>-0.08365661900715038</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.835841473980198</v>
+        <v>-7.576005803524311</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1714302293908023</v>
+        <v>-0.06749596120844803</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.592076031996753</v>
+        <v>-7.332240361540867</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07814334425037428</v>
+        <v>0.02579092393198046</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.328047964803494</v>
+        <v>-7.068212294347607</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.02959219654694589</v>
+        <v>0.1335264647293006</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.078197570854419</v>
+        <v>-6.818361900398532</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1222744291102775</v>
+        <v>0.2262086972926327</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.77463008185044</v>
+        <v>-6.514794411394553</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2473005482325181</v>
+        <v>0.3512348164148729</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.701150172998426</v>
+        <v>-6.441314502542539</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2900200178278771</v>
+        <v>0.3939542860102319</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.476117173329603</v>
+        <v>-6.216281502873716</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3790536953117032</v>
+        <v>0.4829879634940584</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.261482795693197</v>
+        <v>-6.00164712523731</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4696022474205832</v>
+        <v>0.5735365156029384</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.994882438718845</v>
+        <v>-5.735046768262958</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5574366489941198</v>
+        <v>0.6613709171764746</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.754451941913985</v>
+        <v>-5.494616271458098</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6553519243409411</v>
+        <v>0.7592861925232963</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.511661134264539</v>
+        <v>-5.251825463808652</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7563975612355396</v>
+        <v>0.8603318294178943</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.395721284639354</v>
+        <v>-5.135885614183467</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8034520850029536</v>
+        <v>0.9073863531853088</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.083467668462009</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.276698394197081</v>
+        <v>-4.893230025760303</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8480593123998563</v>
+        <v>1.001446659774567</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.083467668462009</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.05667759616007</v>
+        <v>-4.673209227723293</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9376466686252747</v>
+        <v>1.091034015999986</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9422478233940288</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.857428966255261</v>
+        <v>-4.473960597818484</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.033240303389022</v>
+        <v>1.186627650763733</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9422478233940288</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.697913862735891</v>
+        <v>-4.314445494299114</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.098192189237072</v>
+        <v>1.251579536611783</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7827327198746589</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.553241717636154</v>
+        <v>-4.169773349199376</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.166149149838406</v>
+        <v>1.319536497213118</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6380605747749215</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.535472258705198</v>
+        <v>-4.15200389026842</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.08859662549751</v>
+        <v>1.241983972872222</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6202911158439659</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.44867276092619</v>
+        <v>-4.065204392489411</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.14571691793168</v>
+        <v>1.299104265306391</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6202911158439659</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.348980146197178</v>
+        <v>-3.965511777760399</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.185666365196697</v>
+        <v>1.339053712571408</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5205985011149541</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.417350332521188</v>
+        <v>-4.03388196408441</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.169325213141795</v>
+        <v>1.322712560516506</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5113228020787391</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.295933902894712</v>
+        <v>-3.912465534457933</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.208328493624276</v>
+        <v>1.361715840998988</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5113228020787391</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.326927062223417</v>
+        <v>-3.943458693786638</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.020640794933181</v>
+        <v>1.174028142307893</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5113228020787391</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.151452802430947</v>
+        <v>-3.767984433994169</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.095397730841957</v>
+        <v>1.248785078216668</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5113228020787391</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.262389055072196</v>
+        <v>-3.878920686635418</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.051034703672255</v>
+        <v>1.204422051046966</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5113228020787391</v>
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.497736301981837</v>
+        <v>3.871021805543983</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.599966272786478</v>
+        <v>3.017408771284617</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.262389055072196</v>
+        <v>-3.878920686635418</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.051034703672255</v>
+        <v>1.204422051046966</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5113228020787391</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.593030069772846</v>
+        <v>3.010472568270985</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.871021805543983</v>
+        <v>3.871021805543984</v>
       </c>
       <c r="C1941" t="n">
         <v>3.017408771284617</v>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.9%</t>
+          <t>135.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>788.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-549.5%</t>
+          <t>-551.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-255.8%</t>
+          <t>-230.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-159.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.1%</t>
+          <t>-277.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-145.0%</t>
+          <t>-176.0%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.348210917647524</v>
+        <v>-9.236627512310776</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5910743735910748</v>
+        <v>-0.5464410114563751</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.058590475341301</v>
+        <v>-2.947007070004552</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.313412132576902</v>
+        <v>1.380362175778951</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.26814112210972</v>
+        <v>-9.156557716772971</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5596796341551959</v>
+        <v>-0.5150462720204967</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.978520679803497</v>
+        <v>-2.866937274466748</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.360820831120341</v>
+        <v>1.427770874322391</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.034659899880122</v>
+        <v>-8.923076494543373</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4583627164255044</v>
+        <v>-0.4137293542908052</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.745039457573899</v>
+        <v>-2.63345605223715</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.508833993295953</v>
+        <v>1.575784036498002</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.854951369736249</v>
+        <v>-8.7433679643995</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3893715146809145</v>
+        <v>-0.3447381525462148</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.687867953411203</v>
+        <v>-2.576284548074453</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.540244685480611</v>
+        <v>1.607194728682661</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.722675896105361</v>
+        <v>-8.611092490768613</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3410938384815325</v>
+        <v>-0.2964604763468328</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.555592479780316</v>
+        <v>-2.444009074443567</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.61497745640617</v>
+        <v>1.68192749960822</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.532076221432208</v>
+        <v>-8.420492816095459</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2620389079246341</v>
+        <v>-0.2174055457899349</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.253409399770414</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.732152321897698</v>
+        <v>1.799102365099748</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.283076422748627</v>
+        <v>-8.171493017411878</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1495326472275429</v>
+        <v>-0.1048992850928436</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.364992805107164</v>
+        <v>-2.253409399770414</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.745058663121357</v>
+        <v>1.812008706323407</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.388666412521731</v>
+        <v>-8.277083007184983</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3197445727360035</v>
+        <v>-0.2751112106013043</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.358999389543519</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.553728739658276</v>
+        <v>1.620678782860326</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.407401314640328</v>
+        <v>-8.29581790930358</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2786941917063559</v>
+        <v>-0.2340608295716566</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.470582794880268</v>
+        <v>-2.358999389543519</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.602273081535362</v>
+        <v>1.669223124737412</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.259461273232729</v>
+        <v>-8.14787786789598</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3393970978314838</v>
+        <v>-0.2947637356967845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.45026187897171</v>
+        <v>-2.338678473634961</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.494586708392329</v>
+        <v>1.561536751594379</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.132568866797659</v>
+        <v>-8.02098546146091</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2973541215109341</v>
+        <v>-0.2527207593762344</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.211786067199891</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.562008165999893</v>
+        <v>1.628958209201943</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.089020460026967</v>
+        <v>-7.97743705469022</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2868953708977506</v>
+        <v>-0.2422620087630514</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.211786067199891</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.5550475539048</v>
+        <v>1.621997597106849</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.846872066573109</v>
+        <v>-7.735288661236361</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1755736591350643</v>
+        <v>-0.130940297000365</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.211786067199891</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.569509908285943</v>
+        <v>1.636459951487993</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.783642694804761</v>
+        <v>-7.672059289468013</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1557497899685298</v>
+        <v>-0.1111164278338306</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.323369472536641</v>
+        <v>-2.211786067199891</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.564042028745138</v>
+        <v>1.630992071947188</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.597155002427755</v>
+        <v>-7.485571597091007</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.08365661900715038</v>
+        <v>-0.03902325687245156</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.136881780159634</v>
+        <v>-2.025298374822885</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.673432738181919</v>
+        <v>1.740382781383968</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.576005803524311</v>
+        <v>-7.464422398187564</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.06749596120844803</v>
+        <v>-0.02286259907374877</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.004149175919441</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.69382323576131</v>
+        <v>1.760773278963359</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.332240361540867</v>
+        <v>-7.220656956204119</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.02579092393198046</v>
+        <v>0.07042428606667928</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.115732581256191</v>
+        <v>-2.004149175919441</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.689603944108361</v>
+        <v>1.75655398731041</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.068212294347607</v>
+        <v>-6.95662888901086</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1335264647293006</v>
+        <v>0.1781598268639994</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.802283777103488</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.812847497317949</v>
+        <v>1.879797540519998</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.818361900398532</v>
+        <v>-6.706778495061785</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2262086972926327</v>
+        <v>0.2708420594273311</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.802283777103488</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.805589572301651</v>
+        <v>1.8725396155037</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.514794411394553</v>
+        <v>-6.403211006057806</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3512348164148729</v>
+        <v>0.3958681785495717</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.913867182440237</v>
+        <v>-1.802283777103488</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.8091886958223</v>
+        <v>1.876138739024349</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.441314502542539</v>
+        <v>-6.329731097205793</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3939542860102319</v>
+        <v>0.4385876481449307</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.840387273588223</v>
+        <v>-1.728803868251473</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.866604147188062</v>
+        <v>1.933554190390112</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.216281502873716</v>
+        <v>-6.10469809753697</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4829879634940584</v>
+        <v>0.5276213256287567</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.6153542739194</v>
+        <v>-1.503770868582651</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.000644424605652</v>
+        <v>2.067594467807702</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.00164712523731</v>
+        <v>-5.890063719900563</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5735365156029384</v>
+        <v>0.6181698777376372</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.289136490946244</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.134119852241814</v>
+        <v>2.201069895443863</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.735046768262958</v>
+        <v>-5.623463362926211</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6613709171764746</v>
+        <v>0.7060042793111734</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.400719896282993</v>
+        <v>-1.289136490946244</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.115314111025609</v>
+        <v>2.182264154227659</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.494616271458098</v>
+        <v>-5.383032866121351</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7592861925232963</v>
+        <v>0.8039195546579947</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.048705994141383</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.261315485733403</v>
+        <v>2.328265528935453</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.251825463808652</v>
+        <v>-5.140242058471905</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8603318294178943</v>
+        <v>0.9049651915525931</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.160289399478133</v>
+        <v>-1.048705994141383</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.265244799568223</v>
+        <v>2.332194842770273</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.135885614183467</v>
+        <v>-5.02430220884672</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9073863531853088</v>
+        <v>0.9520197153200072</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.083467668462009</v>
+        <v>-0.9718842631252596</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.312016422095238</v>
+        <v>2.378966465297287</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.893230025760303</v>
+        <v>-4.781646620423556</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.001446659774567</v>
+        <v>1.046080021909266</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.083467668462009</v>
+        <v>-0.9718842631252596</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.309014493315231</v>
+        <v>2.375964536517281</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.673209227723293</v>
+        <v>-4.561625822386546</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.091034015999986</v>
+        <v>1.135667378134685</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8306644180572793</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.395325437366633</v>
+        <v>2.462275480568683</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.473960597818484</v>
+        <v>-4.362377192481737</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.186627650763733</v>
+        <v>1.231261012898432</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9422478233940288</v>
+        <v>-0.8306644180572793</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.411219620168457</v>
+        <v>2.478169663370506</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.314445494299114</v>
+        <v>-4.202862088962367</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.251579536611783</v>
+        <v>1.296212898746481</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7827327198746589</v>
+        <v>-0.6711493145379094</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.50807452672038</v>
+        <v>2.57502456992243</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.169773349199376</v>
+        <v>-4.058189943862629</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.319536497213118</v>
+        <v>1.364169859347816</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6380605747749215</v>
+        <v>-0.526477169438172</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.604965916341663</v>
+        <v>2.671915959543712</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.15200389026842</v>
+        <v>-4.040420484931674</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241983972872222</v>
+        <v>1.28661733500692</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5087077105072164</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.530967283786957</v>
+        <v>2.597917326989007</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.065204392489411</v>
+        <v>-3.953620987152665</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299104265306391</v>
+        <v>1.34373762744109</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6202911158439659</v>
+        <v>-0.5087077105072164</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.553367777109524</v>
+        <v>2.620317820311573</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.965511777760399</v>
+        <v>-3.853928372423653</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.339053712571408</v>
+        <v>1.383687074706107</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5205985011149541</v>
+        <v>-0.4090150957782047</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.613255747320343</v>
+        <v>2.680205790522392</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.03388196408441</v>
+        <v>-3.922298558747663</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.322712560516506</v>
+        <v>1.367345922651205</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.3997393967419897</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.629828089216774</v>
+        <v>2.696778132418824</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.912465534457933</v>
+        <v>-3.800882129121186</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.361715840998988</v>
+        <v>1.406349203133687</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.3997393967419897</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.620264797848665</v>
+        <v>2.687214841050715</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.943458693786638</v>
+        <v>-3.831875288449892</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.174028142307893</v>
+        <v>1.218661504442591</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.3997393967419897</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.444974362889052</v>
+        <v>2.511924406091102</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.767984433994169</v>
+        <v>-3.656401028657422</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.248785078216668</v>
+        <v>1.293418440351367</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.3997393967419897</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.44954159488084</v>
+        <v>2.516491638082889</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.878920686635418</v>
+        <v>-3.767337281298671</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.204422051046966</v>
+        <v>1.249055413181665</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.3997393967419897</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.449553068767637</v>
+        <v>2.516503111969687</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.871021805543984</v>
+        <v>3.863992498658808</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.017408771284617</v>
+        <v>3.020949252870333</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.878920686635418</v>
+        <v>-3.902652908664951</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.204422051046966</v>
+        <v>1.459531665090606</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5113228020787391</v>
+        <v>-0.5350550241082694</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.010472568270985</v>
+        <v>2.699916238405372</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240421.xlsx
+++ b/tame_output/ON/bt/strategyON_20240421.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-47.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.1%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.4%</t>
+          <t>-684.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.7%</t>
+          <t>788.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.8%</t>
+          <t>-583.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.3%</t>
+          <t>-268.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.3%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.5%</t>
+          <t>-283.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.0%</t>
+          <t>-218.1%</t>
         </is>
       </c>
     </row>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739581339122513</v>
+        <v>-8.9994170095784</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830531096745626</v>
+        <v>-0.4869873778569174</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122582727865144</v>
+        <v>-9.382418398321031</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.536355766493199</v>
+        <v>-0.6402900346755538</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.497568054036421</v>
+        <v>-9.530214733904801</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.68377838099028</v>
+        <v>-0.696837052937632</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.01565829088653</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.769896896053614</v>
+        <v>1.906210290406118</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.857098376540423</v>
+        <v>-9.889745056408803</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8222402066938304</v>
+        <v>-0.8352988786411824</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.01565829088653</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.775247199351664</v>
+        <v>1.911560593704169</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.18349840520544</v>
+        <v>-10.21614508507382</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9448841982026583</v>
+        <v>-0.9579428701500103</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.56924731013905</v>
+        <v>-2.342058319551543</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.587323202109834</v>
+        <v>1.723636596462338</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.40264737327963</v>
+        <v>-10.43529405314801</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.029502034810568</v>
+        <v>-1.04256070675792</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.56120728762574</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.458875571887084</v>
+        <v>1.595188966239589</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.39895644832322</v>
+        <v>-10.4316031281916</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.028025664828004</v>
+        <v>-1.041084336775356</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.56120728762574</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.458875571887084</v>
+        <v>1.595188966239589</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.60321462365309</v>
+        <v>-10.63586130352147</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.104215737841307</v>
+        <v>-1.117274409788659</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.916035222827236</v>
+        <v>-2.688846232239729</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.387805402237333</v>
+        <v>1.524118796589838</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.82125239528426</v>
+        <v>-10.85389907515264</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.186948292009342</v>
+        <v>-1.200006963956694</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.090805990923135</v>
+        <v>-2.863617000335628</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.28742549586423</v>
+        <v>1.423738890216734</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.74778256361681</v>
+        <v>-10.78042924348519</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.142188657848942</v>
+        <v>-1.155247329796294</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.017336159255687</v>
+        <v>-2.79014716866818</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.34687909635812</v>
+        <v>1.483192490710625</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.92290698100336</v>
+        <v>-10.95555366087174</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.197683204056042</v>
+        <v>-1.210741876003394</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.19246057664223</v>
+        <v>-2.965271586054723</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.256359666673711</v>
+        <v>1.392673061026215</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.15735907501785</v>
+        <v>-11.19000575488623</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.298683206563434</v>
+        <v>-1.311741878510786</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.19246057664223</v>
+        <v>-2.965271586054723</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.249140501772115</v>
+        <v>1.385453896124619</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.44516291955509</v>
+        <v>-11.47780959942347</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.420476935152305</v>
+        <v>-1.433535607099657</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.480264421179469</v>
+        <v>-3.253075430591962</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.069786004275796</v>
+        <v>1.2060993986283</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.67498736671891</v>
+        <v>-11.70763404658729</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.511290924179279</v>
+        <v>-1.524349596126631</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.642911958249629</v>
+        <v>-3.415722967662122</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9733132718722559</v>
+        <v>1.10962666622476</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.90701628645517</v>
+        <v>-11.93966296632355</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.601408763444669</v>
+        <v>-1.614467435392021</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.477735664850545</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9387993821883165</v>
+        <v>1.075112776540821</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.85500077248636</v>
+        <v>-11.88764745235474</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.576612222170743</v>
+        <v>-1.589670894118095</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.477735664850545</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9427897178747173</v>
+        <v>1.079103112227222</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.99667261421048</v>
+        <v>-12.02931929407886</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.634756185759133</v>
+        <v>-1.647814857706485</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.477735664850545</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9413144909759756</v>
+        <v>1.07762788532848</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.09557935466976</v>
+        <v>-12.12822603453814</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.65926547177797</v>
+        <v>-1.672324143725322</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.803831395897328</v>
+        <v>-3.57664240530982</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8970238568652826</v>
+        <v>1.033337251217787</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.89642724743266</v>
+        <v>-11.92907392730104</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.592655762529814</v>
+        <v>-1.605714434477166</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.638508869947514</v>
+        <v>-3.411319879360007</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9831662387884879</v>
+        <v>1.119479633140992</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.67058209471325</v>
+        <v>-11.70322877458162</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.492738628405842</v>
+        <v>-1.505797300353193</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.369393203772844</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.017901317176995</v>
+        <v>1.154214711529499</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.38430728239055</v>
+        <v>-11.41695396225893</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.377089558920705</v>
+        <v>-1.390148230868056</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.369393203772844</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.019040461733054</v>
+        <v>1.155353856085558</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.43720257043484</v>
+        <v>-11.46984925030322</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.395613899976311</v>
+        <v>-1.408672571923662</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.364437857684397</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.024647443548229</v>
+        <v>1.160960837900733</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.15329383950609</v>
+        <v>-11.18594051937447</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.276316703366176</v>
+        <v>-1.289375375313527</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.364437857684397</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.030381147786865</v>
+        <v>1.16669454213937</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.03787291536799</v>
+        <v>-11.07051959523637</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.239885596104802</v>
+        <v>-1.252944268052153</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.249016933546302</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.089896439875857</v>
+        <v>1.226209834228362</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.77403604816392</v>
+        <v>-10.8066827280323</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.144234330536082</v>
+        <v>-1.157293002483433</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.249016933546302</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08001295856295</v>
+        <v>1.216326352915454</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.50679424729553</v>
+        <v>-10.5394409271639</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.039172170688097</v>
+        <v>-1.052230842635448</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.249016933546302</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.078178398063576</v>
+        <v>1.214491792416081</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.38348831881731</v>
+        <v>-10.41613499868568</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.99015011427027</v>
+        <v>-1.003208786217621</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.386788253006246</v>
+        <v>-3.159599262418739</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.131528685766653</v>
+        <v>1.267842080119157</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.35953477784135</v>
+        <v>-10.39218145770973</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.979900191734393</v>
+        <v>-0.9929588636817441</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.362834712030288</v>
+        <v>-3.135645721442781</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.146569316497721</v>
+        <v>1.282882710850226</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.09547483951855</v>
+        <v>-10.12812151938693</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8875365325670259</v>
+        <v>-0.9005952045143779</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.098774773707492</v>
+        <v>-2.871585783119985</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.291744963329647</v>
+        <v>1.428058357682151</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.388395216013715</v>
+        <v>-9.421041895882093</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6074917168253924</v>
+        <v>-0.6205503887727435</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.098774773707492</v>
+        <v>-2.871585783119985</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.288957929669346</v>
+        <v>1.42527132402185</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.236627512310776</v>
+        <v>-9.380857597515902</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5464410114563751</v>
+        <v>-0.604133045538426</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.947007070004552</v>
+        <v>-2.831401484753794</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.380362175778951</v>
+        <v>1.449725526929406</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.156557716772971</v>
+        <v>-9.300787801978098</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5150462720204967</v>
+        <v>-0.5727383061025471</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.866937274466748</v>
+        <v>-2.75133168921599</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.427770874322391</v>
+        <v>1.497134225472845</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.923076494543373</v>
+        <v>-9.0673065797485</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4137293542908052</v>
+        <v>-0.471421388372856</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.63345605223715</v>
+        <v>-2.517850466986391</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.575784036498002</v>
+        <v>1.645147387648457</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.7433679643995</v>
+        <v>-8.887598049604627</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3447381525462148</v>
+        <v>-0.4024301866282656</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.576284548074453</v>
+        <v>-2.460678962823696</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.607194728682661</v>
+        <v>1.676558079833115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.611092490768613</v>
+        <v>-8.755322575973739</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2964604763468328</v>
+        <v>-0.3541525104288836</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.444009074443567</v>
+        <v>-2.328403489192809</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.68192749960822</v>
+        <v>1.751290850758674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.420492816095459</v>
+        <v>-8.564722901300586</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2174055457899349</v>
+        <v>-0.2750975798719857</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.253409399770414</v>
+        <v>-2.137803814519657</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.799102365099748</v>
+        <v>1.868465716250203</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.171493017411878</v>
+        <v>-8.315723102617005</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1048992850928436</v>
+        <v>-0.1625913191748944</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.253409399770414</v>
+        <v>-2.137803814519657</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.812008706323407</v>
+        <v>1.881372057473861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.277083007184983</v>
+        <v>-8.421313092390109</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2751112106013043</v>
+        <v>-0.3328032446833546</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.358999389543519</v>
+        <v>-2.243393804292761</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.620678782860326</v>
+        <v>1.69004213401078</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.29581790930358</v>
+        <v>-8.440047994508706</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2340608295716566</v>
+        <v>-0.2917528636537075</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.358999389543519</v>
+        <v>-2.243393804292761</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.669223124737412</v>
+        <v>1.738586475887866</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.14787786789598</v>
+        <v>-8.292107953101107</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2947637356967845</v>
+        <v>-0.3524557697788353</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.338678473634961</v>
+        <v>-2.223072888384203</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.561536751594379</v>
+        <v>1.630900102744833</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.02098546146091</v>
+        <v>-8.165215546666037</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2527207593762344</v>
+        <v>-0.3104127934582852</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.211786067199891</v>
+        <v>-2.096180481949133</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.628958209201943</v>
+        <v>1.698321560352397</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.97743705469022</v>
+        <v>-8.121667139895345</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2422620087630514</v>
+        <v>-0.2999540428451017</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.211786067199891</v>
+        <v>-2.096180481949133</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.621997597106849</v>
+        <v>1.691360948257304</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.735288661236361</v>
+        <v>-7.879518746441487</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.130940297000365</v>
+        <v>-0.1886323310824154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.211786067199891</v>
+        <v>-2.096180481949133</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.636459951487993</v>
+        <v>1.705823302638447</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.672059289468013</v>
+        <v>-7.816289374673139</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1111164278338306</v>
+        <v>-0.1688084619158809</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.211786067199891</v>
+        <v>-2.096180481949133</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.630992071947188</v>
+        <v>1.700355423097642</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.485571597091007</v>
+        <v>-7.629801682296133</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.03902325687245156</v>
+        <v>-0.09671529095450193</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.025298374822885</v>
+        <v>-1.909692789572127</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.740382781383968</v>
+        <v>1.809746132534423</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.464422398187564</v>
+        <v>-7.60865248339269</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02286259907374877</v>
+        <v>-0.08055463315579914</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.004149175919441</v>
+        <v>-1.888543590668684</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.760773278963359</v>
+        <v>1.830136630113814</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.220656956204119</v>
+        <v>-7.364887041409245</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.07042428606667928</v>
+        <v>0.01273225198462891</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.004149175919441</v>
+        <v>-1.888543590668684</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.75655398731041</v>
+        <v>1.825917338460865</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.95662888901086</v>
+        <v>-7.100858974215985</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1781598268639994</v>
+        <v>0.1204677927819491</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.802283777103488</v>
+        <v>-1.68667819185273</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.879797540519998</v>
+        <v>1.949160891670453</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.706778495061785</v>
+        <v>-6.85100858026691</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2708420594273311</v>
+        <v>0.2131500253452812</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.802283777103488</v>
+        <v>-1.68667819185273</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.8725396155037</v>
+        <v>1.941902966654155</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.403211006057806</v>
+        <v>-6.547441091262932</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3958681785495717</v>
+        <v>0.3381761444675213</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.802283777103488</v>
+        <v>-1.68667819185273</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.876138739024349</v>
+        <v>1.945502090174804</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.329731097205793</v>
+        <v>-6.473961182410918</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4385876481449307</v>
+        <v>0.3808956140628807</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.728803868251473</v>
+        <v>-1.613198283000716</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.933554190390112</v>
+        <v>2.002917541540566</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.10469809753697</v>
+        <v>-6.248928182742095</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5276213256287567</v>
+        <v>0.4699292915467068</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.503770868582651</v>
+        <v>-1.388165283331893</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.067594467807702</v>
+        <v>2.136957818958157</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.890063719900563</v>
+        <v>-6.034293805105688</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6181698777376372</v>
+        <v>0.5604778436555868</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.289136490946244</v>
+        <v>-1.173530905695486</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.201069895443863</v>
+        <v>2.270433246594318</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.623463362926211</v>
+        <v>-5.767693448131336</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7060042793111734</v>
+        <v>0.6483122452291235</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.289136490946244</v>
+        <v>-1.173530905695486</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.182264154227659</v>
+        <v>2.251627505378114</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.383032866121351</v>
+        <v>-5.527262951326476</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8039195546579947</v>
+        <v>0.7462275205759448</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.048705994141383</v>
+        <v>-0.9331004088906258</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.328265528935453</v>
+        <v>2.397628880085907</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.140242058471905</v>
+        <v>-5.28447214367703</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9049651915525931</v>
+        <v>0.8472731574705432</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.048705994141383</v>
+        <v>-0.9331004088906258</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.332194842770273</v>
+        <v>2.401558193920728</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.02430220884672</v>
+        <v>-5.168532294051845</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9520197153200072</v>
+        <v>0.8943276812379573</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9718842631252596</v>
+        <v>-0.856278677874502</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.378966465297287</v>
+        <v>2.448329816447742</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.781646620423556</v>
+        <v>-4.925876705628681</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.046080021909266</v>
+        <v>0.9883879878272164</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9718842631252596</v>
+        <v>-0.856278677874502</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.375964536517281</v>
+        <v>2.445327887667735</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.561625822386546</v>
+        <v>-4.813013201429452</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.135667378134685</v>
+        <v>1.035112426517522</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8306644180572793</v>
+        <v>-0.8244585754504685</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.462275480568683</v>
+        <v>2.46599898613277</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.362377192481737</v>
+        <v>-4.613764571524643</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.231261012898432</v>
+        <v>1.130706061281269</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8306644180572793</v>
+        <v>-0.8244585754504685</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.478169663370506</v>
+        <v>2.481893168934593</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.202862088962367</v>
+        <v>-4.454249468005274</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.296212898746481</v>
+        <v>1.195657947129319</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6711493145379094</v>
+        <v>-0.6649434719310986</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.57502456992243</v>
+        <v>2.578748075486517</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.058189943862629</v>
+        <v>-4.309577322905536</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.364169859347816</v>
+        <v>1.263614907730654</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.526477169438172</v>
+        <v>-0.5202713268313612</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.671915959543712</v>
+        <v>2.675639465107799</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.040420484931674</v>
+        <v>-4.29180786397458</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.28661733500692</v>
+        <v>1.186062383389757</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5087077105072164</v>
+        <v>-0.5025018679004056</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.597917326989007</v>
+        <v>2.601640832553094</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.953620987152665</v>
+        <v>-4.205008366195571</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.34373762744109</v>
+        <v>1.243182675823927</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5087077105072164</v>
+        <v>-0.5025018679004056</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.620317820311573</v>
+        <v>2.62404132587566</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.853928372423653</v>
+        <v>-4.105315751466559</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.383687074706107</v>
+        <v>1.283132123088944</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4090150957782047</v>
+        <v>-0.4028092531713939</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.680205790522392</v>
+        <v>2.683929296086479</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.922298558747663</v>
+        <v>-4.17368593779057</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.367345922651205</v>
+        <v>1.266790971034042</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3997393967419897</v>
+        <v>-0.3935335541351789</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.696778132418824</v>
+        <v>2.70050163798291</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.800882129121186</v>
+        <v>-4.052269508164093</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.406349203133687</v>
+        <v>1.305794251516524</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3997393967419897</v>
+        <v>-0.3935335541351789</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.687214841050715</v>
+        <v>2.690938346614801</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.831875288449892</v>
+        <v>-4.083262667492798</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.218661504442591</v>
+        <v>1.118106552825429</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3997393967419897</v>
+        <v>-0.3935335541351789</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.511924406091102</v>
+        <v>2.515647911655188</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.656401028657422</v>
+        <v>-3.907788407700329</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.293418440351367</v>
+        <v>1.192863488734204</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3997393967419897</v>
+        <v>-0.3935335541351789</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.516491638082889</v>
+        <v>2.520215143646976</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.767337281298671</v>
+        <v>-4.018724660341578</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.249055413181665</v>
+        <v>1.148500461564502</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3997393967419897</v>
+        <v>-0.3935335541351789</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.516503111969687</v>
+        <v>2.520226617533774</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.863992498658808</v>
+        <v>3.861414625799806</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.020949252870333</v>
+        <v>2.638422976565318</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.902652908664951</v>
+        <v>-4.223180017788148</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.459531665090606</v>
+        <v>0.9487945451363113</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5350550241082694</v>
+        <v>-0.5979889115817489</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.699916238405372</v>
+        <v>2.279629629616269</v>
       </c>
     </row>
   </sheetData>
